--- a/SSTSS_GenSim_Modules/Scenario_Selection_Module/list_of_selected_scenarios.xlsx
+++ b/SSTSS_GenSim_Modules/Scenario_Selection_Module/list_of_selected_scenarios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR39"/>
+  <dimension ref="A1:AR53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,7 +652,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC2-S65</t>
+          <t>SC2-S13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Turning lead vehicle</t>
+          <t>Ego vehicle approaching slower lead vehicle</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction while following its lead vehicle. The ego vehicle intends to go straight at the junction while the preceding vehicle turns left or right at the junction. </t>
+          <t>Another vehicle is driving in front of the ego vehicle at a slower speed. As a result, the other vehicle appears in the ego vehicle’s f ield of view. The ego vehicle might brake to avoid a collision.</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -834,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -855,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -903,14 +903,14 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sc65.png</t>
+          <t>sc13.png</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -927,16 +927,16 @@
         <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP3" t="n">
         <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>2</v>
@@ -944,21 +944,21 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SC2-S13</t>
+          <t>SC2-S27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ego vehicle approaching slower lead vehicle</t>
+          <t>Ego vehicle turns right at signalized junction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Another vehicle is driving in front of the ego vehicle at a slower speed. As a result, the other vehicle appears in the ego vehicle’s f ield of view. The ego vehicle might brake to avoid a collision.</t>
+          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The ego vehicle intends to turn right and other vehicle is going straight.</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1001,7 +1001,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1046,17 +1046,17 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sc13.png</t>
+          <t>sc261.png</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1066,14 +1066,14 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Follow Lead Vehicle</t>
+          <t>Crossing Path</t>
         </is>
       </c>
       <c r="AM4" t="n">
         <v>5</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
         <v>4</v>
@@ -1082,7 +1082,7 @@
         <v>5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AR4" t="n">
         <v>3</v>
@@ -1090,21 +1090,21 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SC2-S8</t>
+          <t>SC2-S36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Lead vehicle braking</t>
+          <t>Undertaking at left turn at non-signalized junction</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The ego vehicle is following another vehicle. The other vehicle is referred to as the lead vehicle. The lead vehicle brakes, such that the ego vehicle has to adapt its speed in order to stay at a safe distance from the lead vehicle.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn left at the junction. Another vehicle is driving in the same direction in the left lane next to the ego vehicle. </t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1126,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1192,17 +1192,17 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sc8.png</t>
+          <t>sc36.png</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1212,45 +1212,45 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Follow Lead Vehicle</t>
+          <t>Crossing Path</t>
         </is>
       </c>
       <c r="AM5" t="n">
         <v>5</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP5" t="n">
         <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SC2-S36</t>
+          <t>SC2-S29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Undertaking at left turn at non-signalized junction</t>
+          <t>Oncomingvehicle turns right at non-signalized junction</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn left at the junction. Another vehicle is driving in the same direction in the left lane next to the ego vehicle. </t>
+          <t>The ego vehicle is approaching a junction that is not equipped with traffic light signals. It intended direction of the ego vehicle is not specified. Another vehicle is approaching the junction from the opposite direction. The other vehicle intends to turn right at the junction, such that the trajectories of the other vehicle and the ego vehicle might intersect</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sc36.png</t>
+          <t>sc29.png</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1377,26 +1377,27 @@
         <v>28</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SC2-S27</t>
+          <t>SC2-S35</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ego vehicle turns right at signalized junction</t>
+          <t xml:space="preserve"> Ego and crossing vehicle turn right at non-signalized
+ junction</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The ego vehicle intends to turn right and other vehicle is going straight.</t>
+          <t>The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the left or right side of the ego vehicle. The other vehicle also turns right at the junction, such that the trajectories of the ego vehicle and the other vehicle intersect.</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1484,17 +1485,17 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sc261.png</t>
+          <t>sc35.png</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1523,12 +1524,12 @@
         <v>28</v>
       </c>
       <c r="AR7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1670,26 +1671,27 @@
         <v>28</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SC2-S29</t>
+          <t>SC2-S33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oncomingvehicle turns right at non-signalized junction</t>
+          <t>Vehicle turns right and ends up in same direction as
+ ego vehicle at non-signalized junction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is not equipped with traffic light signals. It intended direction of the ego vehicle is not specified. Another vehicle is approaching the junction from the opposite direction. The other vehicle intends to turn right at the junction, such that the trajectories of the other vehicle and the ego vehicle might intersect</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to go straight at the junction. Another vehicle is approaching the junction from the right side of the ego vehicle. The other vehicle turns right at the junction, such that it ends up in the same direction as the ego vehicle. </t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1787,7 +1789,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sc29.png</t>
+          <t>sc33.png</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -1816,27 +1818,27 @@
         <v>28</v>
       </c>
       <c r="AR9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC2-S33</t>
+          <t>SC2-S34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vehicle turns right and ends up in same direction as
- ego vehicle at non-signalized junction</t>
+          <t>Ego vehicle turns right and ends up in same direction
+ as other vehicle at non-signalized junction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to go straight at the junction. Another vehicle is approaching the junction from the right side of the ego vehicle. The other vehicle turns right at the junction, such that it ends up in the same direction as the ego vehicle. </t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the left side of the ego vehicle. The other vehicle goes straight at the junction, such that it ends up in the same direction as the ego vehicle. </t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1879,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1900,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1934,7 +1936,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sc33.png</t>
+          <t>sc34.png</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -1951,7 +1953,7 @@
         <v>5</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AO10" t="n">
         <v>4</v>
@@ -1960,30 +1962,29 @@
         <v>5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SC2-S35</t>
+          <t>SC2-S9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ego and crossing vehicle turn right at non-signalized
- junction</t>
+          <t>Cut-in in front of the ego vehicle</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the left or right side of the ego vehicle. The other vehicle also turns right at the junction, such that the trajectories of the ego vehicle and the other vehicle intersect.</t>
+          <t xml:space="preserve">Another vehicle is driving in the same direction as the ego vehicle in an adjacent lane. The other vehicle makes a lane change, such that is becomes the lead vehicle from the ego vehicle’s perspective. </t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2074,14 +2075,14 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sc35.png</t>
+          <t>sc9.png</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2091,7 +2092,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Crossing Path</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM11" t="n">
@@ -2115,22 +2116,21 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SC2-S32</t>
+          <t>SC2-S12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Vehicle straight with ego from left at non-signalized
- junction</t>
+          <t>Cut-out in front of the ego vehicle</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junc tion that is not equipped with traffic light signals. Another vehicle is also approaching the junction and its trajectory intersects the ego vehicle’s trajectory. The other vehicle is ap proaching the junction from the right side of the ego vehicle and this vehicle goes straight at the junction.</t>
+          <t>Another vehicle is driving in the same direction as the ego vehicle in front of the ego vehicle such that it is the lead vehicle from the ego vehicle’s perspective. The other vehicle makes a lane change, such that it will no longer be the ego vehicle’s lead vehicle.</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2152,13 +2152,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2221,14 +2221,14 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sc32.png</t>
+          <t>sc12.png</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Crossing Path</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM12" t="n">
@@ -2248,36 +2248,35 @@
         <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP12" t="n">
         <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SC2-S34</t>
+          <t>SC2-S10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ego vehicle turns right and ends up in same direction
- as other vehicle at non-signalized junction</t>
+          <t>Ego performing lane change with vehicle behind</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the left side of the ego vehicle. The other vehicle goes straight at the junction, such that it ends up in the same direction as the ego vehicle. </t>
+          <t>Another vehicle is driving in the same direction as the ego vehicle, in a lane adjacent to the ego vehicle lane. The ego vehicle intends to perform a lane change towards the lane in which the other vehicle is driving</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2332,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2341,7 +2340,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2368,14 +2367,14 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sc34.png</t>
+          <t>sc10.png</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2385,14 +2384,14 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Crossing Path</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM13" t="n">
         <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AO13" t="n">
         <v>4</v>
@@ -2401,29 +2400,29 @@
         <v>5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SC2-S9</t>
+          <t>SC2-S11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cut-in in front of the ego vehicle</t>
+          <t>Ego merging into an occupied lane</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Another vehicle is driving in the same direction as the ego vehicle in an adjacent lane. The other vehicle makes a lane change, such that is becomes the lead vehicle from the ego vehicle’s perspective. </t>
+          <t>The lane adjacent to the ego vehicle lane is occupied by slow driving vehicles. The ego vehicle intends to perform a lane change towards the lane in which the other vehicles are driving.</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2466,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2478,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2521,7 +2520,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sc9.png</t>
+          <t>sc11.png</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2538,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2547,29 +2546,29 @@
         <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AR14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SC2-S12</t>
+          <t>SC2-S20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cut-out in front of the ego vehicle</t>
+          <t>Oncoming vehicle</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Another vehicle is driving in the same direction as the ego vehicle in front of the ego vehicle such that it is the lead vehicle from the ego vehicle’s perspective. The other vehicle makes a lane change, such that it will no longer be the ego vehicle’s lead vehicle.</t>
+          <t xml:space="preserve">The ego vehicle is driving straight while another vehicle drives in opposite direction in the same lane. </t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2667,7 +2666,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sc12.png</t>
+          <t>sc20.png</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2677,7 +2676,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Opposite Direction</t>
         </is>
       </c>
       <c r="AM15" t="n">
@@ -2696,26 +2695,27 @@
         <v>28</v>
       </c>
       <c r="AR15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SC2-S6</t>
+          <t>SC2-S28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Impassable object on intended path</t>
+          <t>Ego vehicle turns right with oncoming vehicle at sig
+nalized junction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The ego vehicle is driving on a road with an object on the intended path of the ego vehicle that is impassable. The initial objective of the ego vehicle is to continue driving straight.</t>
+          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The ego vehicle turns right at the junction. Another vehicle is approaching the junction from the opposite direction. The other vehicle goes straight at the junction, such that the trajectories of the other vehicle and the ego vehicle intersect. The ego vehicle has to give right of way to the other vehicle.</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2737,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2803,17 +2803,17 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sc6.png</t>
+          <t>sc28.png</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -2823,45 +2823,46 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Opposite Direction</t>
         </is>
       </c>
       <c r="AM16" t="n">
         <v>5</v>
       </c>
       <c r="AN16" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AO16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP16" t="n">
         <v>5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SC2-S15</t>
+          <t>SC2-S30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vehicle swerving towards ego vehicle</t>
+          <t xml:space="preserve"> Ego vehicle turns right with oncoming vehicle at non
+signalized junction</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Another vehicle is driving in the same direction as the ego vehicle in an adjacent lane. The other vehicle swerves towards the ego vehicle’s lane.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the opposite direction. The direction that the other vehicle goes to is not specified, i.e., the vehicle could turn left or right or the vehicle could go straight at the junction. </t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2883,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2904,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2925,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2952,14 +2953,14 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sc15.png</t>
+          <t>sc30.png</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -2969,52 +2970,52 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Opposite Direction</t>
         </is>
       </c>
       <c r="AM17" t="n">
         <v>5</v>
       </c>
       <c r="AN17" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP17" t="n">
         <v>5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SC2-S22</t>
+          <t>SC2-S39</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oncoming vehicle swerving into ego vehicle’s lane</t>
+          <t>Jaywalking</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is driving straight while another vehicle drives in opposite direction on a lane next to the ego vehicle lane. The other vehicle starts to swerve towards the lane of the ego vehicle. </t>
+          <t>The ego vehicle is driving on a road with a jaywalker. Although the jaywalker is not allowed to cross the road, the ego vehicle is expected to behave appropriately to avoid critical situations.</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3029,13 +3030,13 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3105,7 +3106,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sc22.png</t>
+          <t>sc39.png</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -3115,52 +3116,54 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN18" t="n">
         <v>14</v>
       </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP18" t="n">
         <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SC2-S11</t>
+          <t>SC2-S44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ego merging into an occupied lane</t>
+          <t>Pedestrian running a red light</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>The lane adjacent to the ego vehicle lane is occupied by slow driving vehicles. The ego vehicle intends to perform a lane change towards the lane in which the other vehicles are driving.</t>
+          <t>The ego vehicle is approaching a pedestrian crossing that is equipped with traffic light signals. The traffic signal for the ego vehicle
+is green. At the same time, a pedestrian is running through the red light. The ego vehicle
+might need to adopt its speed to stay at a safe distance from the pedestrian.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -3196,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3208,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3251,7 +3254,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sc11.png</t>
+          <t>sc44.png</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -3261,14 +3264,14 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AO19" t="n">
         <v>4</v>
@@ -3277,36 +3280,37 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC2-S10</t>
+          <t>SC2-S45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ego performing lane change with vehicle behind</t>
+          <t>Pedestrian crossing from behind an obstruction</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Another vehicle is driving in the same direction as the ego vehicle, in a lane adjacent to the ego vehicle lane. The ego vehicle intends to perform a lane change towards the lane in which the other vehicle is driving</t>
+          <t xml:space="preserve">The ego vehicle is driving on a road while a pedestrian crosses the road. The pedestrian is initially outside the view of the ego
+vehicle due to an obstruction. </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -3342,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -3354,7 +3358,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -3397,7 +3401,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sc10.png</t>
+          <t>sc45.png</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -3407,14 +3411,14 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AO20" t="n">
         <v>4</v>
@@ -3423,182 +3427,187 @@
         <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AR20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>29</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SC2-S40</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Pedestrian crossing at zebra crossing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is approaching a zebra crossing that is not equipped with traffic light signals. At the same time, a pedestrian is crossing the road using the zebra crossing. The ego vehicle has to give right of way to the pedestrian. </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sc40.png</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Pedestrian Interaction</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP21" t="n">
         <v>5</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SC2-S7</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Passable object on intended path</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>The ego vehicle is driving on a road with an object on the intended path of the ego vehicle that is passable, e.g., a manhole lid or a small branch. There are no other vehicles specified. the ego vehicle might swerve around the object, although it also could have driven over it.</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sc7.png</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Lane Change Scenario</t>
-        </is>
-      </c>
-      <c r="AM21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>4</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AR21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SC2-S20</t>
+          <t>SC2-S48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oncoming vehicle</t>
+          <t>Pedestrian in same direction obstructed at ego left turn</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is driving straight while another vehicle drives in opposite direction in the same lane. </t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. It is not specified whether the junction is
+equipped with traffic light signals. A pedestrian is approaching the junction from the same
+direction on the left side of the road (from the perspective of the ego vehicle). The pedestrian
+goes straight at the junction such that the trajectories of the ego vehicle and the pedestrian
+intersect. The view from the ego vehicle to the pedestrian is obstructed, e.g., by bushes or
+a hedge.</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -3634,13 +3643,13 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -3682,14 +3691,14 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sc20.png</t>
+          <t>sc48.png</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3699,14 +3708,14 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Opposite Direction</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
         <v>4</v>
@@ -3715,36 +3724,38 @@
         <v>5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AR22" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SC2-S21</t>
+          <t>SC2-S46</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Object on road with oncoming traffic</t>
+          <t>Pedestrian at left turn at non-signalized junction</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>The ego vehicle is driving while ap proaching an object on the road, e.g., a parked vehicle. At the same time, a vehicle is approaching in opposite direction. To objective of the ego vehicle is to continue driving straight.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. The junction is not equipped with traffic light
+signals. A pedestrian is walking on the left side of the ego vehicle. The walking direction of
+the pedestrian is not specified. </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -3759,10 +3770,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3780,13 +3791,13 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -3828,14 +3839,14 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sc21.png</t>
+          <t>sc46.png</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -3845,53 +3856,58 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Opposite Direction</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN23" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP23" t="n">
         <v>5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AR23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SC2-S28</t>
+          <t>SC2-S49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ego vehicle turns right with oncoming vehicle at sig
-nalized junction</t>
+          <t>Pedestrian at right turn at non-signalized junction</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The ego vehicle turns right at the junction. Another vehicle is approaching the junction from the opposite direction. The other vehicle goes straight at the junction, such that the trajectories of the other vehicle and the ego vehicle intersect. The ego vehicle has to give right of way to the other vehicle.</t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is not equipped with traffic
+light signals. A pedestrian is walking on the right side of the ego vehicle. The walking
+direction of the pedestrian is not specified. Therefore, the pedestrian might walk towards
+the ego vehicle, in the same direction, or perpendicular to the ego vehicle, etc. Because the
+pedestrian is initially on the right side of the ego vehicle while the ego vehicle intends to
+turn right, it might be possible that the trajectories of the pedestrian and the ego vehicle
+intersect.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -3972,17 +3988,17 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sc28.png</t>
+          <t>sc49.png</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -3992,11 +4008,11 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Opposite Direction</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN24" t="n">
         <v>7</v>
@@ -4008,37 +4024,41 @@
         <v>5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR24" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SC2-S30</t>
+          <t>SC2-S50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ego vehicle turns right with oncoming vehicle at non
-signalized junction</t>
+          <t>Pedestrian at right turn at signalized junction</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the opposite direction. The direction that the other vehicle goes to is not specified, i.e., the vehicle could turn left or right or the vehicle could go straight at the junction. </t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is equipped with traffic light
+signals. A pedestrian is walking on the right side of the ego vehicle. The walking direction of
+the pedestrian is not specified. Therefore, the pedestrian might walk towards the ego vehicle,
+in the same direction, or perpendicular to the ego vehicle, etc. Because the pedestrian is
+initially on the right side of the ego vehicle while the ego vehicle intends to turn right, it
+might be possible that the trajectories of the pedestrian and the ego vehicle intersect</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -4119,17 +4139,17 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sc30.png</t>
+          <t>sc50.png</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -4139,11 +4159,11 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Opposite Direction</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN25" t="n">
         <v>7</v>
@@ -4155,34 +4175,36 @@
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SC2-S1</t>
+          <t>SC2-S55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Maneuvering a bend</t>
+          <t>Ego vehicle approaching cyclist riding in same direction</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>The ego vehicle is driving on a curved
- road.</t>
+          <t xml:space="preserve">The ego vehicle is driving towards a cyclist that is riding in the same direction. The initial intention of the ego vehicle is to drive
+straight. To safely pass the cyclist, the ego vehicle might need to divert its path. Another
+possibility is that the ego vehicle brakes such that the ego vehicle stays behind the cyclist.
+</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -4191,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -4221,10 +4243,10 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -4276,7 +4298,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sc1.png</t>
+          <t>sc55.png</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -4286,14 +4308,14 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Turning Scenario</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO26" t="n">
         <v>4</v>
@@ -4302,33 +4324,35 @@
         <v>5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SC2-S2</t>
+          <t>SC2-S67</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turning left</t>
+          <t>Cyclist turning right and ends up in lane of ego vehicle</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The ego vehicle is turnning left at non-signalized junction.</t>
+          <t>The ego vehicle and a cyclist approach a non-signalized junction. The cyclist is coming from the right side of the ego vehicle. The
+ego vehicle intends to go straight while the cyclist turns right at the junction, such that the
+ego vehicle and the cyclist end up in the same lane.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -4337,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -4367,13 +4391,13 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -4422,7 +4446,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sc2.png</t>
+          <t>sc67.png</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -4432,14 +4456,14 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Turning Scenario</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -4448,141 +4472,143 @@
         <v>5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR27" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
+        <v>50</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SC2-S66</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cyclist turning left and ends up in lane of ego vehicle</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>The ego vehicle and a cyclist approach a non-signalized junction. The cyclist is coming from the left side of the ego vehicle. The
+ego vehicle intends to go straight while the cyclist turns left at the junction, such that the
+ego vehicle and the cyclist end up in the same lane.</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sc66.png</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM28" t="n">
         <v>2</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SC2-S4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Driving straight</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>The ego vehicle is driving on a straight road.</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sc4.png</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Miscellaneous</t>
-        </is>
-      </c>
-      <c r="AM28" t="n">
-        <v>5</v>
       </c>
       <c r="AN28" t="n">
         <v>14</v>
@@ -4591,36 +4617,38 @@
         <v>4</v>
       </c>
       <c r="AP28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR28" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SC2-S3</t>
+          <t>SC2-S51</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turning Right</t>
+          <t>Cyclist crossing from the left side at non-signalized junction</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The ego vehicle is turning right at non-signalized junction.</t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is not equipped with traffic
+light signals. A cyclist is approaching the junction from the left of the ego vehicle. The
+trajectories of the ego vehicle and the cyclist intersect.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4629,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -4659,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -4680,7 +4708,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4714,7 +4742,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>sc3.png</t>
+          <t>sc51.png</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -4724,14 +4752,14 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Turning Scenario</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN29" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
         <v>4</v>
@@ -4740,33 +4768,35 @@
         <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AR29" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SC2-S23</t>
+          <t>SC2-S52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ego vehicle approaching red traffic light</t>
+          <t>Cyclist crossing from right side at non-signalized junction</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is red. The objective of the ego vehicle is to cross the junction, but because the traffic signal is red, the ego vehicle is expected to stop.</t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is not equipped with traffic
+light signals. A cyclist is approaching the junction from the right of the ego vehicle. The
+trajectories of the ego vehicle and the cyclist intersect.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4775,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -4850,17 +4880,17 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>sc23.png</t>
+          <t>sc52.png</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -4870,11 +4900,11 @@
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Traffic Signal</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN30" t="n">
         <v>14</v>
@@ -4886,33 +4916,35 @@
         <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AR30" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SC2-S17</t>
+          <t>SC2-S53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Stopping at a bus bay</t>
+          <t>Cyclist crossing from left side at signalized junction</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a bus bay. The goal of the ego vehicle is to park at the bus bay. </t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is equipped with traffic light
+signals. A cyclist is approaching the junction from the left of the ego vehicle. The trajectories
+of the ego vehicle and the cyclist intersect.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4921,7 +4953,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -4996,17 +5028,17 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sc17.png</t>
+          <t>sc53.png</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -5016,11 +5048,11 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN31" t="n">
         <v>14</v>
@@ -5032,33 +5064,35 @@
         <v>5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SC2-S19</t>
+          <t>SC2-S54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Driving along a bus bay</t>
+          <t>Cyclist crossing from right side at signalized junction</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>The ego vehicle passes a bus bay. The goal of the ego vehicle is to continue driving. There might be another vehicle at the bus bay intending to leave the bus bay.</t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is equipped with traffic
+light signals. A cyclist is approaching the junction from the right of the ego vehicle. The
+trajectories of the ego vehicle and the cyclist intersect.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -5067,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -5142,17 +5176,17 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>sc19.png</t>
+          <t>sc54.png</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -5162,11 +5196,11 @@
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN32" t="n">
         <v>14</v>
@@ -5178,33 +5212,36 @@
         <v>5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AR32" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SC2-S16</t>
+          <t>SC2-S56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vehicle backing up into ego vehicle</t>
+          <t>Ego vehicle driving alongside a cyclist</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Another vehicle is driving in reverse. This could be, for example as shown in Figure 35a, because the vehicle is being parked. It might be the case that the ego vehicle has to respond to the reversing vehicle,</t>
+          <t>The ego vehicle is driving straight while a cyclist is riding on the left side of the road in the same direction as the ego vehicle. This
+might be because the ego vehicle is overtaking a cyclist. Alternatively, it is also possible
+that the cyclist overtakes the ego vehicle from the left. To prevent a collision between the
+ego vehicle and the cyclist, the ego vehicle might need to divert its path.</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -5213,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -5222,10 +5259,10 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5288,17 +5325,17 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>sc16.png</t>
+          <t>sc56.png</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -5308,49 +5345,51 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN33" t="n">
         <v>14</v>
       </c>
       <c r="AO33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP33" t="n">
         <v>5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AR33" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SC2-S5</t>
+          <t>SC2-S63</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Navigating on an empty roundabout</t>
+          <t>Entering a roundabout with a cyclist</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a round about. There are no other actors at the roundabout. The ego vehicle wants to navigate the roundabout in any of the possible directions. </t>
+          <t xml:space="preserve">The ego vehicle is approaching a roundabout. There is a cyclist on the roundabout or a cyclist is approaching the roundabout
+from another direction. In any case, because the junction is a roundabout, the other vehicle
+approaches the ego vehicle from the right. </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -5359,7 +5398,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -5389,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -5407,7 +5446,7 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
@@ -5434,17 +5473,17 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sc5.png</t>
+          <t>sc63.png</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -5454,14 +5493,14 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>Turning Scenario</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN34" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AO34" t="n">
         <v>4</v>
@@ -5470,33 +5509,35 @@
         <v>5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AR34" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SC2-S18</t>
+          <t>SC2-S57</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Leaving a bus bay</t>
+          <t>Cyclist and ego vehicle driving in opposite direction</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>The ego vehicle is initially stationary at a bus bay. The goal of the ego vehicle is to leave the bus bay.</t>
+          <t xml:space="preserve">The ego vehicle is driving in the opposite direction of a cyclist. Therefore, the ego vehicle is expected to slow down or to stop when
+the cyclist is passing the ego vehicle, although the initial objective of the ego vehicle is to
+continue driving. </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5505,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -5535,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -5550,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -5590,7 +5631,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>sc18.png</t>
+          <t>sc57.png</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -5600,14 +5641,14 @@
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN35" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AO35" t="n">
         <v>4</v>
@@ -5616,33 +5657,35 @@
         <v>5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR35" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SC2-S26</t>
+          <t>SC2-S58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vehicle running red traffic light</t>
+          <t>Cyclist at left turn at non-signalized junction</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is green. Another vehicle is also approaching the junction and its trajectory intersects that of the ego vehicle. The traffic signal for the other vehicle is red. However, the vehicle is running through the red light. </t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. The junction is not equipped with traffic light
+signals. A cyclist is riding on the left side of the ego vehicle. The riding direction of the
+cyclist is not specified. </t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -5651,7 +5694,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -5681,13 +5724,13 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -5726,17 +5769,17 @@
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sc26.png</t>
+          <t>sc58.png</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -5746,14 +5789,14 @@
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Traffic Signal</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN36" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO36" t="n">
         <v>4</v>
@@ -5762,33 +5805,38 @@
         <v>5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AR36" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SC2-S24</t>
+          <t>SC2-S59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ego vehicle approaching green traffic light</t>
+          <t>Cyclist at left turn at signalized junction</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is green or turns green. The objective of the ego vehicle is to cross the junction.</t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. The junction is equipped with traffic light
+signals. A cyclist is riding on the left side of the ego vehicle. The riding direction of the
+cyclist is not specified. Therefore, the cyclist might ride towards the ego vehicle, in the same
+direction, or perpendicular to the ego vehicle, etc. Because the cyclist is initially on the left
+side of the ego vehicle while the ego vehicle intends to turn left, it might be possible that
+the trajectories of the cyclist and the ego vehicle intersect.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -5797,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -5827,13 +5875,13 @@
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5882,7 +5930,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>sc24.png</t>
+          <t>sc59.png</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -5892,14 +5940,14 @@
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Traffic Signal</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN37" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO37" t="n">
         <v>4</v>
@@ -5908,33 +5956,38 @@
         <v>5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AR37" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SC2-S25</t>
+          <t>SC2-S60</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ego vehicle approaching amber traffic light</t>
+          <t>Cyclist driving in same direction obstructed at ego left turn</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is amber or turns amber. The objective of the ego vehicle is to cross the junction.</t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. It is not specified whether the junction is
+equipped with traffic light signals. A cyclist is approaching the junction from the same
+direction on the left side of the road (from the perspective of the ego vehicle). The cyclist
+goes straight at the junction such that the trajectories of the ego vehicle and the cyclist
+intersect. The view from the ego vehicle to the cyclist is obstructed, e.g., by bushes or a
+hedge.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -5943,7 +5996,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -5973,13 +6026,13 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -6018,17 +6071,17 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sc25.png</t>
+          <t>sc60.png</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -6038,14 +6091,14 @@
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Traffic Signal</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN38" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO38" t="n">
         <v>4</v>
@@ -6054,33 +6107,35 @@
         <v>5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AR38" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SC2-S37</t>
+          <t>SC2-S64</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Entering a roundabout with another vehicle</t>
+          <t>Leaving a roundabout with a cyclist</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a round about. There is another vehicle on the roundabout or another vehicle is approaching the roundabout from another direction.</t>
+          <t>The ego vehicle is leaving a roundabout. There is a cyclist on the roundabout. In case the cyclist does not leave the roundabout at
+the same exit as the ego vehicle does, it might be that the ego vehicle needs to give priority
+to the cyclist.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -6089,7 +6144,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -6119,13 +6174,13 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -6174,7 +6229,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>sc37.png</t>
+          <t>sc64.png</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -6184,14 +6239,14 @@
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN39" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO39" t="n">
         <v>4</v>
@@ -6200,10 +6255,2065 @@
         <v>5</v>
       </c>
       <c r="AQ39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>46</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SC2-S61</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cyclist at right turn at non-signalized junction</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is not equipped with traffic
+light signals. A cyclist is riding on the right side of the ego vehicle. The riding direction
+of the cyclist is not specified. Therefore, the cyclist might ride towards the ego vehicle, in
+the same direction, or perpendicular to the ego vehicle, etc. Because the cyclist is initially
+on the right side of the ego vehicle while the ego vehicle intends to turn right, it might be
+possible that the trajectories of the cyclist and the ego vehicle intersect.</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sc61.png</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>47</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SC2-S62</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Cyclist at left turn at signalized junction</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is equipped with traffic light
+signals. A cyclist is riding on the right side of the ego vehicle. The riding direction of the
+cyclist is not specified. Therefore, the cyclist might ride towards the ego vehicle, in the same
+direction, or perpendicular to the ego vehicle, etc. Because the cyclist is initially on the right
+side of the ego vehicle while the ego vehicle intends to turn right, it might be possible that
+the trajectories of the cyclist and the ego vehicle intersect.</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sc62.png</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SC2-S1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Maneuvering a bend</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>The ego vehicle is driving on a curved
+ road.</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sc1.png</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Turning Scenario</t>
+        </is>
+      </c>
+      <c r="AM42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SC2-S2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Turning left</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>The ego vehicle is turning left at non-signalized junction.</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sc2.png</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Turning Scenario</t>
+        </is>
+      </c>
+      <c r="AM43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SC2-S5</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Navigating on an empty roundabout</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is approaching a round about. There are no other actors at the roundabout. The ego vehicle wants to navigate the roundabout in any of the possible directions. </t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sc5.png</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Turning Scenario</t>
+        </is>
+      </c>
+      <c r="AM44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SC2-S3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Turning Right</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>The ego vehicle is turning right at non-signalized junction.</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sc3.png</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>Turning Scenario</t>
+        </is>
+      </c>
+      <c r="AM45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SC2-S17</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Stopping at a bus bay</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is approaching a bus bay. The goal of the ego vehicle is to park at the bus bay. </t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sc17.png</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="AM46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ46" t="n">
         <v>28</v>
       </c>
-      <c r="AR39" t="n">
-        <v>24</v>
+      <c r="AR46" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>11</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SC2-S19</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Driving along a bus bay</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>The ego vehicle passes a bus bay. The goal of the ego vehicle is to continue driving. There might be another vehicle at the bus bay intending to leave the bus bay.</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sc19.png</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="AM47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>13</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SC2-S23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ego vehicle approaching red traffic light</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is red. The objective of the ego vehicle is to cross the junction, but because the traffic signal is red, the ego vehicle is expected to stop.</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sc23.png</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Traffic Signal</t>
+        </is>
+      </c>
+      <c r="AM48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SC2-S18</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Leaving a bus bay</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>The ego vehicle is initially stationary at a bus bay. The goal of the ego vehicle is to leave the bus bay.</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sc18.png</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="AM49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>14</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SC2-S24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ego vehicle approaching green traffic light</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is green or turns green. The objective of the ego vehicle is to cross the junction.</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sc24.png</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Traffic Signal</t>
+        </is>
+      </c>
+      <c r="AM50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>15</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SC2-S25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ego vehicle approaching amber traffic light</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is amber or turns amber. The objective of the ego vehicle is to cross the junction.</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sc25.png</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Traffic Signal</t>
+        </is>
+      </c>
+      <c r="AM51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>16</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SC2-S26</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Vehicle running red traffic light</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is green. Another vehicle is also approaching the junction and its trajectory intersects that of the ego vehicle. The traffic signal for the other vehicle is red. However, the vehicle is running through the red light. </t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sc26.png</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Traffic Signal</t>
+        </is>
+      </c>
+      <c r="AM52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>26</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SC2-S37</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Entering a roundabout with another vehicle</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a round about. There is another vehicle on the roundabout or another vehicle is approaching the roundabout from another direction.</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sc37.png</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="AM53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/SSTSS_GenSim_Modules/Scenario_Selection_Module/list_of_selected_scenarios.xlsx
+++ b/SSTSS_GenSim_Modules/Scenario_Selection_Module/list_of_selected_scenarios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR53"/>
+  <dimension ref="A1:AR40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,21 +652,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SC2-S14</t>
+          <t>SCNHTSA-S31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ego vehicle approaching stopped lead vehicle</t>
+          <t>Lane Change Right</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A lead vehicle driving in front of the ego vehicle at a slower speed . The reason for the other vehicle to come to a full stop is, e.g., because of a traffic light. The objective of the ego vehicle is to continue driving in the same direction.</t>
+          <t>Driver of Vehicle A looked for traffic before changing lanes to the right on a four-lane road. The driver did not see Vehicle B in the curb lane. Vehicle B braked and steered to avoid Vehicle A.</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -762,19 +762,15 @@
       <c r="AI2" t="n">
         <v>1</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>sc14.png</t>
-        </is>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Follow Lead Vehicle</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -798,21 +794,21 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SC2-S13</t>
+          <t>SCNHTSA-S23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ego vehicle approaching slower lead vehicle</t>
+          <t>Avoidance, Rear</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Another vehicle is driving in front of the ego vehicle at a slower speed. As a result, the other vehicle appears in the ego vehicle’s f ield of view. The ego vehicle might brake to avoid a collision.</t>
+          <t>Vehicle A observed traffic slowing in the curb lane. A decided to change lanes and go around slowing traffic. A changed lanes to the inside lane only to find Vehicle B stopped directly in front. Driver A could not stop and struck B in the rear. (This also includes cases of three cars in the same lane. The middle vehicle pulled out of the lane at the last moment leaving the rear-most vehicle to collide with the foremost.)</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -867,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -879,7 +875,7 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -908,26 +904,22 @@
       <c r="AI3" t="n">
         <v>1</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sc13.png</t>
-        </is>
-      </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Follow Lead Vehicle</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO3" t="n">
         <v>4</v>
@@ -936,7 +928,7 @@
         <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AR3" t="n">
         <v>2</v>
@@ -944,21 +936,21 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SC2-S27</t>
+          <t>SCNHTSA-S33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ego vehicle turns right at signalized junction</t>
+          <t>Lane Change Left</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The ego vehicle intends to turn right and other vehicle is going straight.</t>
+          <t>Driver of Vehicle A looked for traffic before changing lanes to the left on a four-lane road. The driver did not see Vehicle B in the next lane. Vehicle B had no time to react and nowhere to go to avoid Vehicle A.</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1001,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1013,7 +1005,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1046,34 +1038,30 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sc261.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Crossing Path</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM4" t="n">
         <v>5</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AO4" t="n">
         <v>4</v>
@@ -1082,29 +1070,29 @@
         <v>5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AR4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SC2-S36</t>
+          <t>SCNHTSA-S34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Undertaking at left turn at non-signalized junction</t>
+          <t>Lane Change, Rear</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn left at the junction. Another vehicle is driving in the same direction in the left lane next to the ego vehicle. </t>
+          <t>Vehicle A saw Vehicle B approaching in the next lane. A determined that B was far enough back that A could change lanes. Driver A misjudged the distance and speed of Vehicle B. B could not stop and struck A; Vehicle C also struck B.</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1147,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1159,7 +1147,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1195,31 +1183,27 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sc36.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Crossing Path</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM5" t="n">
         <v>5</v>
       </c>
       <c r="AN5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AO5" t="n">
         <v>4</v>
@@ -1228,36 +1212,36 @@
         <v>5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AR5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SC2-S29</t>
+          <t>SCNHTSA-S1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oncomingvehicle turns right at non-signalized junction</t>
+          <t>Struck Human</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is not equipped with traffic light signals. It intended direction of the ego vehicle is not specified. Another vehicle is approaching the junction from the opposite direction. The other vehicle intends to turn right at the junction, such that the trajectories of the other vehicle and the ego vehicle might intersect</t>
+          <t>A pedestrian crossing a multi-lane roadway was struck by vehicle. The driver was looking for other vehicles and traffic controls, but did not see the pedestrian. This crash occurs more frequently in urban areas. The weather is typically clear and the road is usually dry.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1341,28 +1325,24 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sc29.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Crossing Path</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN6" t="n">
         <v>14</v>
@@ -1374,7 +1354,7 @@
         <v>5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR6" t="n">
         <v>3</v>
@@ -1382,22 +1362,21 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SC2-S35</t>
+          <t>SCNHTSA-S39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ego and crossing vehicle turn right at non-signalized
- junction</t>
+          <t>Slick Road, head-on</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the left or right side of the ego vehicle. The other vehicle also turns right at the junction, such that the trajectories of the ego vehicle and the other vehicle intersect.</t>
+          <t>Vehicle A attempted to stop at an intersection, but because of the slick road, lost control. Vehicle B was approaching head-on and was struck by A.</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1488,24 +1467,20 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sc35.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Crossing Path</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM7" t="n">
@@ -1524,27 +1499,26 @@
         <v>28</v>
       </c>
       <c r="AR7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SC2-S31</t>
+          <t>SCNHTSA-S38</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ego straight with vehicle from left at non-signalized
- junction</t>
+          <t>Impaired, Head-on</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The objective of the ego vehicle is to go straight at the junction. Another vehicle is approaching the junction from the left side of the ego vehicle. The direction of the other vehicle is not further specified. </t>
+          <t>A young male driver A, who was legally impaired, was driving too fast. He lost control of the vehicle, crossed the centerline, and struck an approaching vehicle head-on.</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1635,24 +1609,20 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sc31.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Crossing Path</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM8" t="n">
@@ -1671,27 +1641,26 @@
         <v>28</v>
       </c>
       <c r="AR8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SC2-S33</t>
+          <t>SCNHTSA-S37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vehicle turns right and ends up in same direction as
- ego vehicle at non-signalized junction</t>
+          <t>Inexperience, Departure</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to go straight at the junction. Another vehicle is approaching the junction from the right side of the ego vehicle. The other vehicle turns right at the junction, such that it ends up in the same direction as the ego vehicle. </t>
+          <t>Driver A was having a difficult time controlling the vehicle on the slippery road. The driver lost control of the vehicle while starting into a curve and applied the brakes. The vehicle crossed into opposite direction traffic and collided head-on with Vehicle B.</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1782,24 +1751,20 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>sc33.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Crossing Path</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM9" t="n">
@@ -1818,27 +1783,26 @@
         <v>28</v>
       </c>
       <c r="AR9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SC2-S34</t>
+          <t>SCNHTSA-S36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ego vehicle turns right and ends up in same direction
- as other vehicle at non-signalized junction</t>
+          <t>U-Turn</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the left side of the ego vehicle. The other vehicle goes straight at the junction, such that it ends up in the same direction as the ego vehicle. </t>
+          <t>Vehicle A and Vehicle B were both heading in the same direction on a multi-lane road in different lanes. B attempted to turn from the curb lane across the path of A onto a side street. Driver A struck illegally turning B.</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1881,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1902,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
@@ -1929,31 +1893,27 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sc34.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Crossing Path</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM10" t="n">
         <v>5</v>
       </c>
       <c r="AN10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
         <v>4</v>
@@ -1962,7 +1922,7 @@
         <v>5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AR10" t="n">
         <v>4</v>
@@ -1970,21 +1930,21 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SC2-S9</t>
+          <t>SCNHTSA-S26</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cut-in in front of the ego vehicle</t>
+          <t>Stutter Stop</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Another vehicle is driving in the same direction as the ego vehicle in an adjacent lane. The other vehicle makes a lane change, such that is becomes the lead vehicle from the ego vehicle’s perspective. </t>
+          <t>A stopped vehicle, A, was looking left and right down a cross road waiting for traffic to clear before proceeding. Another driver, B, waiting behind A was also checking crossing traffic. Vehicle A started to go, decided that it wasn't safe, and abruptly stopped. Driver B rear-ended A.</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2075,24 +2035,20 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sc9.png</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr"/>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM11" t="n">
@@ -2111,26 +2067,26 @@
         <v>28</v>
       </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SC2-S12</t>
+          <t>SCNHTSA-S22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cut-out in front of the ego vehicle</t>
+          <t>Distracted, Rear</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Another vehicle is driving in the same direction as the ego vehicle in front of the ego vehicle such that it is the lead vehicle from the ego vehicle’s perspective. The other vehicle makes a lane change, such that it will no longer be the ego vehicle’s lead vehicle.</t>
+          <t>The driver of Vehicle A was reaching down to retrieve an item from the floor of the vehicle and did not notice that Vehicle B was stopped ahead.</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2226,19 +2182,15 @@
       <c r="AI12" t="n">
         <v>1</v>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sc12.png</t>
-        </is>
-      </c>
+      <c r="AJ12" t="inlineStr"/>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM12" t="n">
@@ -2257,26 +2209,26 @@
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SC2-S10</t>
+          <t>SCNHTSA-S21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ego performing lane change with vehicle behind</t>
+          <t>Tailgate</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Another vehicle is driving in the same direction as the ego vehicle, in a lane adjacent to the ego vehicle lane. The ego vehicle intends to perform a lane change towards the lane in which the other vehicle is driving</t>
+          <t>Vehicle B was following Vehicle A too closely. Vehicle A had to stop quickly; B could not stop in time and rear-ended A.</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2319,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2331,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -2372,26 +2324,22 @@
       <c r="AI13" t="n">
         <v>1</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sc10.png</t>
-        </is>
-      </c>
+      <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM13" t="n">
         <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
         <v>4</v>
@@ -2400,29 +2348,29 @@
         <v>5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AR13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SC2-S11</t>
+          <t>SCNHTSA-S17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ego merging into an occupied lane</t>
+          <t>Wrong Driveway</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>The lane adjacent to the ego vehicle lane is occupied by slow driving vehicles. The ego vehicle intends to perform a lane change towards the lane in which the other vehicles are driving.</t>
+          <t>Driver A observed Vehicle B approaching with the right turn signal on. A assumed that B was turning into the driveway that A was turning out of and proceeded in front of B. B was not turning until the intersection and struck A in the side.</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2465,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2477,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
@@ -2510,34 +2458,30 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sc11.png</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr"/>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM14" t="n">
         <v>5</v>
       </c>
       <c r="AN14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2546,29 +2490,29 @@
         <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AR14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SC2-S20</t>
+          <t>SCNHTSA-S19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oncoming vehicle</t>
+          <t>Turn into Passer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is driving straight while another vehicle drives in opposite direction in the same lane. </t>
+          <t>An impatient driver, A, was following behind a slower vehicle, B. Driver A passed vehicle B. Driver B turned left as A was passing and collided with A.</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2664,19 +2608,15 @@
       <c r="AI15" t="n">
         <v>1</v>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sc20.png</t>
-        </is>
-      </c>
+      <c r="AJ15" t="inlineStr"/>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Opposite Direction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM15" t="n">
@@ -2695,27 +2635,26 @@
         <v>28</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SC2-S28</t>
+          <t>SCNHTSA-S43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ego vehicle turns right with oncoming vehicle at sig
-nalized junction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The ego vehicle turns right at the junction. Another vehicle is approaching the junction from the opposite direction. The other vehicle goes straight at the junction, such that the trajectories of the other vehicle and the ego vehicle intersect. The ego vehicle has to give right of way to the other vehicle.</t>
+          <t>This is a miscellaneous assortment that could not be classified as any other previously mentioned crash descriptions.</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2758,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -2779,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2803,34 +2742,30 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sc28.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Opposite Direction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM16" t="n">
         <v>5</v>
       </c>
       <c r="AN16" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AO16" t="n">
         <v>4</v>
@@ -2839,30 +2774,29 @@
         <v>5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AR16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SC2-S30</t>
+          <t>SCNHTSA-S11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ego vehicle turns right with oncoming vehicle at non
-signalized junction</t>
+          <t>Slick Road, Ran Stop</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the opposite direction. The direction that the other vehicle goes to is not specified, i.e., the vehicle could turn left or right or the vehicle could go straight at the junction. </t>
+          <t>As vehicle approached an intersection, the driver noticed the stop sign, applied the brakes hard, but slid on the wet pavement into crossing traffic. (This group does not include the condition where there is no sign.)</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2905,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -2926,7 +2860,7 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2958,26 +2892,22 @@
       <c r="AI17" t="n">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>sc30.png</t>
-        </is>
-      </c>
+      <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Opposite Direction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM17" t="n">
         <v>5</v>
       </c>
       <c r="AN17" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
         <v>4</v>
@@ -2986,36 +2916,36 @@
         <v>5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SC2-S39</t>
+          <t>SCNHTSA-S3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jaywalking</t>
+          <t>Drowsy</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>The ego vehicle is driving on a road with a jaywalker. Although the jaywalker is not allowed to cross the road, the ego vehicle is expected to behave appropriately to avoid critical situations.</t>
+          <t>The driver fell asleep and drifted off the right side of the road and struck a telephone pole. Witnesses say that there was no attempt to brake or steer away from the pole. The crash occurred in a rural area at night.</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -3045,7 +2975,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3104,23 +3034,19 @@
       <c r="AI18" t="n">
         <v>1</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sc39.png</t>
-        </is>
-      </c>
+      <c r="AJ18" t="inlineStr"/>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Pedestrian Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN18" t="n">
         <v>14</v>
@@ -3132,38 +3058,36 @@
         <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SC2-S44</t>
+          <t>SCNHTSA-S4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pedestrian running a red light</t>
+          <t>Aggressive, Departure</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a pedestrian crossing that is equipped with traffic light signals. The traffic signal for the ego vehicle
-is green. At the same time, a pedestrian is running through the red light. The ego vehicle
-might need to adopt its speed to stay at a safe distance from the pedestrian.</t>
+          <t>The male driver was driving too fast, as well as cutting in and out of traffic, maneuvering the vehicle to the limits of control. The driver lost control of the vehicle and went into a skid. The driver left the roadway and struck the guardrail and then a tree.</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -3252,23 +3176,19 @@
       <c r="AI19" t="n">
         <v>1</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>sc44.png</t>
-        </is>
-      </c>
+      <c r="AJ19" t="inlineStr"/>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Pedestrian Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN19" t="n">
         <v>14</v>
@@ -3280,37 +3200,36 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SC2-S45</t>
+          <t>SCNHTSA-S10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pedestrian crossing from behind an obstruction</t>
+          <t>Ran Red “T- Bone”</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is driving on a road while a pedestrian crosses the road. The pedestrian is initially outside the view of the ego
-vehicle due to an obstruction. </t>
+          <t>Driver ran the red light. The driver saw the light turn yellow but decided to continue through the intersection. The majority of these crashes occur during daylight hours in urban areas.</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -3399,23 +3318,19 @@
       <c r="AI20" t="n">
         <v>1</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>sc45.png</t>
-        </is>
-      </c>
+      <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Pedestrian Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN20" t="n">
         <v>14</v>
@@ -3427,36 +3342,36 @@
         <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SC2-S40</t>
+          <t>SCNHTSA-S6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pedestrian crossing at zebra crossing</t>
+          <t>Rough Road Departure</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a zebra crossing that is not equipped with traffic light signals. At the same time, a pedestrian is crossing the road using the zebra crossing. The ego vehicle has to give right of way to the pedestrian. </t>
+          <t>Due to the patched and eroded condition of the road surface, the driver lost control of the vehicle and left the roadway.</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -3545,23 +3460,19 @@
       <c r="AI21" t="n">
         <v>1</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>sc40.png</t>
-        </is>
-      </c>
+      <c r="AJ21" t="inlineStr"/>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Pedestrian Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN21" t="n">
         <v>14</v>
@@ -3573,41 +3484,36 @@
         <v>5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR21" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SC2-S48</t>
+          <t>SCNHTSA-S12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pedestrian in same direction obstructed at ego left turn</t>
+          <t>Inattentive, Ran Stop</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. It is not specified whether the junction is
-equipped with traffic light signals. A pedestrian is approaching the junction from the same
-direction on the left side of the road (from the perspective of the ego vehicle). The pedestrian
-goes straight at the junction such that the trajectories of the ego vehicle and the pedestrian
-intersect. The view from the ego vehicle to the pedestrian is obstructed, e.g., by bushes or
-a hedge.</t>
+          <t>An inattentive driver in a vehicle, heading north, did not see a stop sign (two-way only) and struck an eastbound vehicle on the passenger's side.</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -3643,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -3691,31 +3597,27 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sc48.png</t>
-        </is>
-      </c>
+      <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Pedestrian Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>4</v>
@@ -3724,38 +3626,36 @@
         <v>5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AR22" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SC2-S46</t>
+          <t>SCNHTSA-S8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pedestrian at left turn at non-signalized junction</t>
+          <t>Impaired, Departure</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. The junction is not equipped with traffic light
-signals. A pedestrian is walking on the left side of the ego vehicle. The walking direction of
-the pedestrian is not specified. </t>
+          <t>The young (under 25) male driver, who was legally impaired, was driving too fast. He lost control of the vehicle, which left the roadway and overturned. The crash occurred in a rural area between midnight and 2 a.m. on a weekend.</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -3782,22 +3682,22 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -3839,75 +3739,65 @@
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sc46.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="inlineStr"/>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Pedestrian Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO23" t="n">
         <v>4</v>
       </c>
       <c r="AP23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SC2-S49</t>
+          <t>SCNHTSA-S16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pedestrian at right turn at non-signalized junction</t>
+          <t>Left Turn Clip</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is not equipped with traffic
-light signals. A pedestrian is walking on the right side of the ego vehicle. The walking
-direction of the pedestrian is not specified. Therefore, the pedestrian might walk towards
-the ego vehicle, in the same direction, or perpendicular to the ego vehicle, etc. Because the
-pedestrian is initially on the right side of the ego vehicle while the ego vehicle intends to
-turn right, it might be possible that the trajectories of the pedestrian and the ego vehicle
-intersect.</t>
+          <t>Vehicle A, in an attempt to turn left, cut the corner too sharply and clipped Vehicle B waiting at the intersection. Vehicle A began the turn too early and misjudged the distance between cars.</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -3949,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3964,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3988,34 +3878,30 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sc49.png</t>
-        </is>
-      </c>
+      <c r="AJ24" t="inlineStr"/>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Pedestrian Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN24" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
         <v>4</v>
@@ -4024,41 +3910,36 @@
         <v>5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AR24" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SC2-S50</t>
+          <t>SCNHTSA-S40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pedestrian at right turn at signalized junction</t>
+          <t>Run Red Into Left Turner</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is equipped with traffic light
-signals. A pedestrian is walking on the right side of the ego vehicle. The walking direction of
-the pedestrian is not specified. Therefore, the pedestrian might walk towards the ego vehicle,
-in the same direction, or perpendicular to the ego vehicle, etc. Because the pedestrian is
-initially on the right side of the ego vehicle while the ego vehicle intends to turn right, it
-might be possible that the trajectories of the pedestrian and the ego vehicle intersect</t>
+          <t>A northbound vehicle, A, was waiting to make a left turn. The light changed and A began to turn left. A southbound driver, B, accelerated hard, hoping to make the light and struck Vehicle A.</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -4100,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -4115,7 +3996,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4139,34 +4020,30 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>sc50.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="inlineStr"/>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Pedestrian Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
@@ -4175,36 +4052,33 @@
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AR25" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SC2-S55</t>
+          <t>SCNHTSA-S30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ego vehicle approaching cyclist riding in same direction</t>
+          <t>Passing Clip</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is driving towards a cyclist that is riding in the same direction. The initial intention of the ego vehicle is to drive
-straight. To safely pass the cyclist, the ego vehicle might need to divert its path. Another
-possibility is that the ego vehicle brakes such that the ego vehicle stays behind the cyclist.
-</t>
+          <t>Vehicle A, in an attempt to pass vehicle B, cut around B, but too closely. Driver A misjudged the distance between cars and clipped the corner of B.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -4213,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -4243,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -4252,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4296,26 +4170,22 @@
       <c r="AI26" t="n">
         <v>1</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sc55.png</t>
-        </is>
-      </c>
+      <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AO26" t="n">
         <v>4</v>
@@ -4327,32 +4197,30 @@
         <v>25</v>
       </c>
       <c r="AR26" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SC2-S67</t>
+          <t>SCNHTSA-S5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cyclist turning right and ends up in lane of ego vehicle</t>
+          <t>Slick Road Departure</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The ego vehicle and a cyclist approach a non-signalized junction. The cyclist is coming from the right side of the ego vehicle. The
-ego vehicle intends to go straight while the cyclist turns right at the junction, such that the
-ego vehicle and the cyclist end up in the same lane.</t>
+          <t>The driver lost control while driving on an icy, wet road. The driver tried to bring the vehicle back under control by braking and steering. The vehicle spun out and came to rest in the ditch.</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -4361,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -4370,22 +4238,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4439,68 +4307,62 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>sc67.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN27" t="n">
         <v>14</v>
       </c>
       <c r="AO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="n">
         <v>4</v>
       </c>
-      <c r="AP27" t="n">
-        <v>5</v>
-      </c>
       <c r="AQ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SC2-S66</t>
+          <t>SCNHTSA-S41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cyclist turning left and ends up in lane of ego vehicle</t>
+          <t>Misjudgment, Left Turn</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>The ego vehicle and a cyclist approach a non-signalized junction. The cyclist is coming from the left side of the ego vehicle. The
-ego vehicle intends to go straight while the cyclist turns left at the junction, such that the
-ego vehicle and the cyclist end up in the same lane.</t>
+          <t>Vehicle A was waiting to turn left. Driver A observed B approaching from the opposite direction, but thought there was enough time. Driver A misjudged B’s distance and was struck.</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -4509,7 +4371,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -4539,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -4554,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -4584,34 +4446,30 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sc66.png</t>
-        </is>
-      </c>
+      <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN28" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AO28" t="n">
         <v>4</v>
@@ -4620,35 +4478,33 @@
         <v>5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SC2-S51</t>
+          <t>SCNHTSA-S27</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cyclist crossing from the left side at non-signalized junction</t>
+          <t>Aggressive, Rear</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is not equipped with traffic
-light signals. A cyclist is approaching the junction from the left of the ego vehicle. The
-trajectories of the ego vehicle and the cyclist intersect.</t>
+          <t>Vehicle A was stopped in traffic. Driver B (at a distance from A) was driving too fast. By the time B realized he/she needed to stop, it was not possible.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4657,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -4687,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -4702,7 +4558,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -4735,31 +4591,27 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>sc51.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="inlineStr"/>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN29" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AO29" t="n">
         <v>4</v>
@@ -4768,35 +4620,33 @@
         <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SC2-S52</t>
+          <t>SCNHTSA-S25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cyclist crossing from right side at non-signalized junction</t>
+          <t>Inattentive, Rear</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is not equipped with traffic
-light signals. A cyclist is approaching the junction from the right of the ego vehicle. The
-trajectories of the ego vehicle and the cyclist intersect.</t>
+          <t>A northbound vehicle, A, was stopped waiting at a red traffic signal in an urban area on a major artery. Another vehicle, B, coming from some distance behind, didn't notice that A was stopped and could not stop in time.</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -4805,7 +4655,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -4835,7 +4685,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -4850,7 +4700,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -4880,34 +4730,30 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>sc52.png</t>
-        </is>
-      </c>
+      <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN30" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AO30" t="n">
         <v>4</v>
@@ -4916,35 +4762,33 @@
         <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SC2-S53</t>
+          <t>SCNHTSA-S42</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cyclist crossing from left side at signalized junction</t>
+          <t>View Obstructed Left Turn</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is equipped with traffic light
-signals. A cyclist is approaching the junction from the left of the ego vehicle. The trajectories
-of the ego vehicle and the cyclist intersect.</t>
+          <t>Vehicle A was stopped in the left lane of a four-lane road. Vehicle C was stopped opposite also turning left. Driver A could see only a short distance past C, thought it was clear, and turned. Vehicle B, in curb lane, struck A head-on.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -4953,7 +4797,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -4983,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -4998,7 +4842,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -5036,26 +4880,22 @@
       <c r="AI31" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>sc53.png</t>
-        </is>
-      </c>
+      <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN31" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AO31" t="n">
         <v>4</v>
@@ -5064,35 +4904,33 @@
         <v>5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SC2-S54</t>
+          <t>SCNHTSA-S18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cyclist crossing from right side at signalized junction</t>
+          <t>Wave to Go</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is equipped with traffic
-light signals. A cyclist is approaching the junction from the right of the ego vehicle. The
-trajectories of the ego vehicle and the cyclist intersect.</t>
+          <t>From a driveway, Vehicle A was waiting to make a left turn, but full view of all lanes was not possible due to other traffic. Driver B stopped—leaving a gap—and waved driver A through in front of him. However, Driver C was unaware of this arrangement and crashed into the driver's side of Vehicle A.</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -5101,7 +4939,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -5131,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -5146,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -5176,34 +5014,30 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>sc54.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ32" t="inlineStr"/>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN32" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AO32" t="n">
         <v>4</v>
@@ -5212,36 +5046,33 @@
         <v>5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR32" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SC2-S56</t>
+          <t>SCNHTSA-S28</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ego vehicle driving alongside a cyclist</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>The ego vehicle is driving straight while a cyclist is riding on the left side of the road in the same direction as the ego vehicle. This
-might be because the ego vehicle is overtaking a cyclist. Alternatively, it is also possible
-that the cyclist overtakes the ego vehicle from the left. To prevent a collision between the
-ego vehicle and the cyclist, the ego vehicle might need to divert its path.</t>
+          <t>Vehicle A was stopped prior to turning when struck by Vehicle B. Driver B stated that the brakes failed to stop the car. Vehicle B was an older vehicle (more than six years).</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -5250,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -5280,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -5295,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -5325,34 +5156,30 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>sc56.png</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr"/>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN33" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AO33" t="n">
         <v>4</v>
@@ -5361,35 +5188,33 @@
         <v>5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AR33" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SC2-S63</t>
+          <t>SCNHTSA-S14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Entering a roundabout with a cyclist</t>
+          <t>Looked but Didn’t See</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a roundabout. There is a cyclist on the roundabout or a cyclist is approaching the roundabout
-from another direction. In any case, because the junction is a roundabout, the other vehicle
-approaches the ego vehicle from the right. </t>
+          <t>Vehicle A was turning right at a two-way stop sign. The driver did not see Vehicle B approaching from lateral direction as Vehicle A turned into the lane. Upon turning, Vehicle A was struck by Vehicle B.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -5398,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -5428,7 +5253,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -5449,7 +5274,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5481,26 +5306,22 @@
       <c r="AI34" t="n">
         <v>0</v>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>sc63.png</t>
-        </is>
-      </c>
+      <c r="AJ34" t="inlineStr"/>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN34" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AO34" t="n">
         <v>4</v>
@@ -5509,35 +5330,33 @@
         <v>5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AR34" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SC2-S57</t>
+          <t>SCNHTSA-S35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cyclist and ego vehicle driving in opposite direction</t>
+          <t>Back Track Front</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is driving in the opposite direction of a cyclist. Therefore, the ego vehicle is expected to slow down or to stop when
-the cyclist is passing the ego vehicle, although the initial objective of the ego vehicle is to
-continue driving. </t>
+          <t>Vehicle A stopped too far out in an intersection. Driver A did not see Vehicle B and backed up to allow other traffic through, striking Vehicle B.</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -5546,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -5576,7 +5395,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -5609,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5621,34 +5440,30 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH35" t="n">
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>sc57.png</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr"/>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN35" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AO35" t="n">
         <v>4</v>
@@ -5657,35 +5472,33 @@
         <v>5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AR35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SC2-S58</t>
+          <t>SCNHTSA-S9</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyclist at left turn at non-signalized junction</t>
+          <t>Back Into Object</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. The junction is not equipped with traffic light
-signals. A cyclist is riding on the left side of the ego vehicle. The riding direction of the
-cyclist is not specified. </t>
+          <t>Vehicle A was backing out of a driveway and struck Vehicle B that was parked along the side of the road. Driver A did not see the other vehicle.</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -5694,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -5730,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -5757,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5772,31 +5585,27 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>sc58.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ36" t="inlineStr"/>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AO36" t="n">
         <v>4</v>
@@ -5805,38 +5614,33 @@
         <v>5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AR36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SC2-S59</t>
+          <t>SCNHTSA-S20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cyclist at left turn at signalized junction</t>
+          <t>Back into Roadway</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. The junction is equipped with traffic light
-signals. A cyclist is riding on the left side of the ego vehicle. The riding direction of the
-cyclist is not specified. Therefore, the cyclist might ride towards the ego vehicle, in the same
-direction, or perpendicular to the ego vehicle, etc. Because the cyclist is initially on the left
-side of the ego vehicle while the ego vehicle intends to turn left, it might be possible that
-the trajectories of the cyclist and the ego vehicle intersect.</t>
+          <t>Driver A backed vehicle into roadway. Driver A did not see vehicle B heading west.</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -5845,7 +5649,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -5881,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -5908,7 +5712,7 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5920,34 +5724,30 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>sc59.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="inlineStr"/>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN37" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AO37" t="n">
         <v>4</v>
@@ -5956,38 +5756,33 @@
         <v>5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AR37" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SC2-S60</t>
+          <t>SCNHTSA-S24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyclist driving in same direction obstructed at ego left turn</t>
+          <t>Pedal Miss</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. It is not specified whether the junction is
-equipped with traffic light signals. A cyclist is approaching the junction from the same
-direction on the left side of the road (from the perspective of the ego vehicle). The cyclist
-goes straight at the junction such that the trajectories of the ego vehicle and the cyclist
-intersect. The view from the ego vehicle to the cyclist is obstructed, e.g., by bushes or a
-hedge.</t>
+          <t>Driver A was attempting to stop behind Vehicle B when Driver A's foot missed the brake pedal and Vehicle A struck Vehicle B from behind.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -5996,7 +5791,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -6032,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -6050,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -6074,31 +5869,27 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>sc60.png</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AJ38" t="inlineStr"/>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN38" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>4</v>
@@ -6107,35 +5898,33 @@
         <v>5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AR38" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SC2-S64</t>
+          <t>SCNHTSA-S15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Leaving a roundabout with a cyclist</t>
+          <t>Sirens</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>The ego vehicle is leaving a roundabout. There is a cyclist on the roundabout. In case the cyclist does not leave the roundabout at
-the same exit as the ego vehicle does, it might be that the ego vehicle needs to give priority
-to the cyclist.</t>
+          <t>A police car, with lights and siren on, slowed to cross through an intersection with a red light. Another vehicle was on the crossing road and did not see the approaching police car.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -6144,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -6180,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -6198,7 +5987,7 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6219,34 +6008,30 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>sc64.png</t>
-        </is>
-      </c>
+      <c r="AJ39" t="inlineStr"/>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN39" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>4</v>
@@ -6255,38 +6040,33 @@
         <v>5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AR39" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SC2-S61</t>
+          <t>SCNHTSA-S29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cyclist at right turn at non-signalized junction</t>
+          <t>Slick Road, Rear</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is not equipped with traffic
-light signals. A cyclist is riding on the right side of the ego vehicle. The riding direction
-of the cyclist is not specified. Therefore, the cyclist might ride towards the ego vehicle, in
-the same direction, or perpendicular to the ego vehicle, etc. Because the cyclist is initially
-on the right side of the ego vehicle while the ego vehicle intends to turn right, it might be
-possible that the trajectories of the cyclist and the ego vehicle intersect.</t>
+          <t>Vehicle A was braking for stopped traffic. Driver B, coming from some distance behind A, saw the brake lights. When B braked the road was very slick. B did not stop and struck A in the rear.</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -6295,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -6304,10 +6084,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -6346,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -6370,1950 +6150,42 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>sc61.png</t>
-        </is>
-      </c>
+      <c r="AJ40" t="inlineStr"/>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>NHTSA</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
-          <t>Cyclist Interaction</t>
+          <t>Miscellaneous</t>
         </is>
       </c>
       <c r="AM40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP40" t="n">
         <v>5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AR40" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>47</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SC2-S62</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Cyclist at left turn at signalized junction</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is equipped with traffic light
-signals. A cyclist is riding on the right side of the ego vehicle. The riding direction of the
-cyclist is not specified. Therefore, the cyclist might ride towards the ego vehicle, in the same
-direction, or perpendicular to the ego vehicle, etc. Because the cyclist is initially on the right
-side of the ego vehicle while the ego vehicle intends to turn right, it might be possible that
-the trajectories of the cyclist and the ego vehicle intersect.</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sc62.png</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>Cyclist Interaction</t>
-        </is>
-      </c>
-      <c r="AM41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>SC2-S1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Maneuvering a bend</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>The ego vehicle is driving on a curved
- road.</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sc1.png</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>Turning Scenario</t>
-        </is>
-      </c>
-      <c r="AM42" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN42" t="n">
         <v>13</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>0</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>SC2-S2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Turning left</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>The ego vehicle is turning left at non-signalized junction.</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>1</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sc2.png</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>Turning Scenario</t>
-        </is>
-      </c>
-      <c r="AM43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>SC2-S5</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Navigating on an empty roundabout</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The ego vehicle is approaching a round about. There are no other actors at the roundabout. The ego vehicle wants to navigate the roundabout in any of the possible directions. </t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>sc5.png</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>Turning Scenario</t>
-        </is>
-      </c>
-      <c r="AM44" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>1</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SC2-S3</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Turning Right</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>The ego vehicle is turning right at non-signalized junction.</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>1</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sc3.png</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>Turning Scenario</t>
-        </is>
-      </c>
-      <c r="AM45" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>9</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>SC2-S17</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Stopping at a bus bay</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The ego vehicle is approaching a bus bay. The goal of the ego vehicle is to park at the bus bay. </t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sc17.png</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Miscellaneous</t>
-        </is>
-      </c>
-      <c r="AM46" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>11</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>SC2-S19</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Driving along a bus bay</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>The ego vehicle passes a bus bay. The goal of the ego vehicle is to continue driving. There might be another vehicle at the bus bay intending to leave the bus bay.</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>sc19.png</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Miscellaneous</t>
-        </is>
-      </c>
-      <c r="AM47" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>13</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>SC2-S23</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Ego vehicle approaching red traffic light</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is red. The objective of the ego vehicle is to cross the junction, but because the traffic signal is red, the ego vehicle is expected to stop.</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>sc23.png</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Traffic Signal</t>
-        </is>
-      </c>
-      <c r="AM48" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>10</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>SC2-S18</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Leaving a bus bay</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>The ego vehicle is initially stationary at a bus bay. The goal of the ego vehicle is to leave the bus bay.</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>sc18.png</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>Miscellaneous</t>
-        </is>
-      </c>
-      <c r="AM49" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>23</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>14</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>SC2-S24</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ego vehicle approaching green traffic light</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is green or turns green. The objective of the ego vehicle is to cross the junction.</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>sc24.png</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Traffic Signal</t>
-        </is>
-      </c>
-      <c r="AM50" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>15</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>SC2-S25</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Ego vehicle approaching amber traffic light</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is amber or turns amber. The objective of the ego vehicle is to cross the junction.</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sc25.png</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>Traffic Signal</t>
-        </is>
-      </c>
-      <c r="AM51" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>16</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>SC2-S26</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Vehicle running red traffic light</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is green. Another vehicle is also approaching the junction and its trajectory intersects that of the ego vehicle. The traffic signal for the other vehicle is red. However, the vehicle is running through the red light. </t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sc26.png</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Traffic Signal</t>
-        </is>
-      </c>
-      <c r="AM52" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO52" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP52" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>26</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>SC2-S37</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Entering a roundabout with another vehicle</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>The ego vehicle is approaching a round about. There is another vehicle on the roundabout or another vehicle is approaching the roundabout from another direction.</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>1</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sc37.png</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Miscellaneous</t>
-        </is>
-      </c>
-      <c r="AM53" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>28</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/SSTSS_GenSim_Modules/Scenario_Selection_Module/list_of_selected_scenarios.xlsx
+++ b/SSTSS_GenSim_Modules/Scenario_Selection_Module/list_of_selected_scenarios.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR40"/>
+  <dimension ref="A1:AR67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -652,21 +652,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SCNHTSA-S31</t>
+          <t>SC2-S14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lane Change Right</t>
+          <t>Ego vehicle approaching stopped lead vehicle</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Driver of Vehicle A looked for traffic before changing lanes to the right on a four-lane road. The driver did not see Vehicle B in the curb lane. Vehicle B braked and steered to avoid Vehicle A.</t>
+          <t>A lead vehicle driving in front of the ego vehicle at a slower speed . The reason for the other vehicle to come to a full stop is, e.g., because of a traffic light. The objective of the ego vehicle is to continue driving in the same direction.</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -762,15 +762,19 @@
       <c r="AI2" t="n">
         <v>1</v>
       </c>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sc14.png</t>
+        </is>
+      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Follow Lead Vehicle</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -794,21 +798,21 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SCNHTSA-S23</t>
+          <t>SC2-S65</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Avoidance, Rear</t>
+          <t>Turning lead vehicle</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vehicle A observed traffic slowing in the curb lane. A decided to change lanes and go around slowing traffic. A changed lanes to the inside lane only to find Vehicle B stopped directly in front. Driver A could not stop and struck B in the rear. (This also includes cases of three cars in the same lane. The middle vehicle pulled out of the lane at the last moment leaving the rear-most vehicle to collide with the foremost.)</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction while following its lead vehicle. The ego vehicle intends to go straight at the junction while the preceding vehicle turns left or right at the junction. </t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -830,10 +834,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -851,7 +855,7 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -863,7 +867,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -899,36 +903,40 @@
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sc65.png</t>
+        </is>
+      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Follow Lead Vehicle</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>5</v>
       </c>
       <c r="AN3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP3" t="n">
         <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AR3" t="n">
         <v>2</v>
@@ -936,21 +944,21 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SCNHTSA-S33</t>
+          <t>SC2-S13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lane Change Left</t>
+          <t>Ego vehicle approaching slower lead vehicle</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Driver of Vehicle A looked for traffic before changing lanes to the left on a four-lane road. The driver did not see Vehicle B in the next lane. Vehicle B had no time to react and nowhere to go to avoid Vehicle A.</t>
+          <t>Another vehicle is driving in front of the ego vehicle at a slower speed. As a result, the other vehicle appears in the ego vehicle’s f ield of view. The ego vehicle might brake to avoid a collision.</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1005,7 +1013,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1017,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1046,22 +1054,26 @@
       <c r="AI4" t="n">
         <v>1</v>
       </c>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sc13.png</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Follow Lead Vehicle</t>
         </is>
       </c>
       <c r="AM4" t="n">
         <v>5</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>4</v>
@@ -1070,29 +1082,29 @@
         <v>5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SCNHTSA-S34</t>
+          <t>SC2-S8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lane Change, Rear</t>
+          <t xml:space="preserve"> Lead vehicle braking</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vehicle A saw Vehicle B approaching in the next lane. A determined that B was far enough back that A could change lanes. Driver A misjudged the distance and speed of Vehicle B. B could not stop and struck A; Vehicle C also struck B.</t>
+          <t>The ego vehicle is following another vehicle. The other vehicle is referred to as the lead vehicle. The lead vehicle brakes, such that the ego vehicle has to adapt its speed in order to stay at a safe distance from the lead vehicle.</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1114,10 +1126,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1147,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1159,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1180,68 +1192,73 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sc8.png</t>
+        </is>
+      </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Lane Change Scenario</t>
+          <t>Follow Lead Vehicle</t>
         </is>
       </c>
       <c r="AM5" t="n">
         <v>5</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR5" t="n">
         <v>4</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SCNHTSA-S1</t>
+          <t>SC2-S33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Struck Human</t>
+          <t>Vehicle turns right and ends up in same direction as
+ ego vehicle at non-signalized junction</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A pedestrian crossing a multi-lane roadway was struck by vehicle. The driver was looking for other vehicles and traffic controls, but did not see the pedestrian. This crash occurs more frequently in urban areas. The weather is typically clear and the road is usually dry.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to go straight at the junction. Another vehicle is approaching the junction from the right side of the ego vehicle. The other vehicle turns right at the junction, such that it ends up in the same direction as the ego vehicle. </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1325,24 +1342,28 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sc33.png</t>
+        </is>
+      </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Pedestrian Interaction</t>
+          <t>Crossing Path</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN6" t="n">
         <v>14</v>
@@ -1354,29 +1375,29 @@
         <v>5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SCNHTSA-S39</t>
+          <t>SC2-S27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Slick Road, head-on</t>
+          <t>Ego vehicle turns right at signalized junction</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Vehicle A attempted to stop at an intersection, but because of the slick road, lost control. Vehicle B was approaching head-on and was struck by A.</t>
+          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The ego vehicle intends to turn right and other vehicle is going straight.</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1464,23 +1485,27 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sc261.png</t>
+        </is>
+      </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Crossing Path</t>
         </is>
       </c>
       <c r="AM7" t="n">
@@ -1499,26 +1524,26 @@
         <v>28</v>
       </c>
       <c r="AR7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SCNHTSA-S38</t>
+          <t>SC2-S29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Impaired, Head-on</t>
+          <t>Oncomingvehicle turns right at non-signalized junction</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A young male driver A, who was legally impaired, was driving too fast. He lost control of the vehicle, crossed the centerline, and struck an approaching vehicle head-on.</t>
+          <t>The ego vehicle is approaching a junction that is not equipped with traffic light signals. It intended direction of the ego vehicle is not specified. Another vehicle is approaching the junction from the opposite direction. The other vehicle intends to turn right at the junction, such that the trajectories of the other vehicle and the ego vehicle might intersect</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1609,20 +1634,24 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>sc29.png</t>
+        </is>
+      </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Crossing Path</t>
         </is>
       </c>
       <c r="AM8" t="n">
@@ -1641,26 +1670,26 @@
         <v>28</v>
       </c>
       <c r="AR8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SCNHTSA-S37</t>
+          <t>SC2-S36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inexperience, Departure</t>
+          <t>Undertaking at left turn at non-signalized junction</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Driver A was having a difficult time controlling the vehicle on the slippery road. The driver lost control of the vehicle while starting into a curve and applied the brakes. The vehicle crossed into opposite direction traffic and collided head-on with Vehicle B.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn left at the junction. Another vehicle is driving in the same direction in the left lane next to the ego vehicle. </t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1751,20 +1780,24 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sc36.png</t>
+        </is>
+      </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Crossing Path</t>
         </is>
       </c>
       <c r="AM9" t="n">
@@ -1783,26 +1816,27 @@
         <v>28</v>
       </c>
       <c r="AR9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SCNHTSA-S36</t>
+          <t>SC2-S31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>U-Turn</t>
+          <t>Ego straight with vehicle from left at non-signalized
+ junction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vehicle A and Vehicle B were both heading in the same direction on a multi-lane road in different lanes. B attempted to turn from the curb lane across the path of A onto a side street. Driver A struck illegally turning B.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The objective of the ego vehicle is to go straight at the junction. Another vehicle is approaching the junction from the left side of the ego vehicle. The direction of the other vehicle is not further specified. </t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1893,20 +1927,24 @@
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sc31.png</t>
+        </is>
+      </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Crossing Path</t>
         </is>
       </c>
       <c r="AM10" t="n">
@@ -1925,26 +1963,27 @@
         <v>28</v>
       </c>
       <c r="AR10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SCNHTSA-S26</t>
+          <t>SC2-S35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Stutter Stop</t>
+          <t xml:space="preserve"> Ego and crossing vehicle turn right at non-signalized
+ junction</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>A stopped vehicle, A, was looking left and right down a cross road waiting for traffic to clear before proceeding. Another driver, B, waiting behind A was also checking crossing traffic. Vehicle A started to go, decided that it wasn't safe, and abruptly stopped. Driver B rear-ended A.</t>
+          <t>The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the left or right side of the ego vehicle. The other vehicle also turns right at the junction, such that the trajectories of the ego vehicle and the other vehicle intersect.</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -2040,15 +2079,19 @@
       <c r="AI11" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sc35.png</t>
+        </is>
+      </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Crossing Path</t>
         </is>
       </c>
       <c r="AM11" t="n">
@@ -2067,26 +2110,27 @@
         <v>28</v>
       </c>
       <c r="AR11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SCNHTSA-S22</t>
+          <t>SC2-S32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Distracted, Rear</t>
+          <t xml:space="preserve"> Vehicle straight with ego from left at non-signalized
+ junction</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The driver of Vehicle A was reaching down to retrieve an item from the floor of the vehicle and did not notice that Vehicle B was stopped ahead.</t>
+          <t>The ego vehicle is approaching a junc tion that is not equipped with traffic light signals. Another vehicle is also approaching the junction and its trajectory intersects the ego vehicle’s trajectory. The other vehicle is ap proaching the junction from the right side of the ego vehicle and this vehicle goes straight at the junction.</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -2108,13 +2152,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2177,20 +2221,24 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sc32.png</t>
+        </is>
+      </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Crossing Path</t>
         </is>
       </c>
       <c r="AM12" t="n">
@@ -2200,35 +2248,36 @@
         <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
         <v>5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SCNHTSA-S21</t>
+          <t>SC2-S34</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tailgate</t>
+          <t>Ego vehicle turns right and ends up in same direction
+ as other vehicle at non-signalized junction</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Vehicle B was following Vehicle A too closely. Vehicle A had to stop quickly; B could not stop in time and rear-ended A.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the left side of the ego vehicle. The other vehicle goes straight at the junction, such that it ends up in the same direction as the ego vehicle. </t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2271,7 +2320,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2292,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2319,27 +2368,31 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sc34.png</t>
+        </is>
+      </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Crossing Path</t>
         </is>
       </c>
       <c r="AM13" t="n">
         <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AO13" t="n">
         <v>4</v>
@@ -2348,29 +2401,29 @@
         <v>5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SCNHTSA-S17</t>
+          <t>SC2-S12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wrong Driveway</t>
+          <t>Cut-out in front of the ego vehicle</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Driver A observed Vehicle B approaching with the right turn signal on. A assumed that B was turning into the driveway that A was turning out of and proceeded in front of B. B was not turning until the intersection and struck A in the side.</t>
+          <t>Another vehicle is driving in the same direction as the ego vehicle in front of the ego vehicle such that it is the lead vehicle from the ego vehicle’s perspective. The other vehicle makes a lane change, such that it will no longer be the ego vehicle’s lead vehicle.</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2458,23 +2511,27 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sc12.png</t>
+        </is>
+      </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM14" t="n">
@@ -2493,26 +2550,26 @@
         <v>28</v>
       </c>
       <c r="AR14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SCNHTSA-S19</t>
+          <t>SC2-S9</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turn into Passer</t>
+          <t>Cut-in in front of the ego vehicle</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>An impatient driver, A, was following behind a slower vehicle, B. Driver A passed vehicle B. Driver B turned left as A was passing and collided with A.</t>
+          <t xml:space="preserve">Another vehicle is driving in the same direction as the ego vehicle in an adjacent lane. The other vehicle makes a lane change, such that is becomes the lead vehicle from the ego vehicle’s perspective. </t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2608,15 +2665,19 @@
       <c r="AI15" t="n">
         <v>1</v>
       </c>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sc9.png</t>
+        </is>
+      </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM15" t="n">
@@ -2635,26 +2696,26 @@
         <v>28</v>
       </c>
       <c r="AR15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SCNHTSA-S43</t>
+          <t>SC2-S6</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Impassable object on intended path</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>This is a miscellaneous assortment that could not be classified as any other previously mentioned crash descriptions.</t>
+          <t>The ego vehicle is driving on a road with an object on the intended path of the ego vehicle that is impassable. The initial objective of the ego vehicle is to continue driving straight.</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2676,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2750,15 +2811,19 @@
       <c r="AI16" t="n">
         <v>1</v>
       </c>
-      <c r="AJ16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sc6.png</t>
+        </is>
+      </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM16" t="n">
@@ -2768,35 +2833,35 @@
         <v>14</v>
       </c>
       <c r="AO16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP16" t="n">
         <v>5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SCNHTSA-S11</t>
+          <t>SC2-S15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slick Road, Ran Stop</t>
+          <t>Vehicle swerving towards ego vehicle</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>As vehicle approached an intersection, the driver noticed the stop sign, applied the brakes hard, but slid on the wet pavement into crossing traffic. (This group does not include the condition where there is no sign.)</t>
+          <t>Another vehicle is driving in the same direction as the ego vehicle in an adjacent lane. The other vehicle swerves towards the ego vehicle’s lane.</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2818,10 +2883,10 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2887,20 +2952,24 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sc15.png</t>
+        </is>
+      </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM17" t="n">
@@ -2910,35 +2979,35 @@
         <v>14</v>
       </c>
       <c r="AO17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP17" t="n">
         <v>5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SCNHTSA-S3</t>
+          <t>SC2-S22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Drowsy</t>
+          <t>Oncoming vehicle swerving into ego vehicle’s lane</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>The driver fell asleep and drifted off the right side of the road and struck a telephone pole. Witnesses say that there was no attempt to brake or steer away from the pole. The crash occurred in a rural area at night.</t>
+          <t xml:space="preserve">The ego vehicle is driving straight while another vehicle drives in opposite direction on a lane next to the ego vehicle lane. The other vehicle starts to swerve towards the lane of the ego vehicle. </t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2960,13 +3029,13 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2975,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -3034,15 +3103,19 @@
       <c r="AI18" t="n">
         <v>1</v>
       </c>
-      <c r="AJ18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sc22.png</t>
+        </is>
+      </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM18" t="n">
@@ -3052,35 +3125,35 @@
         <v>14</v>
       </c>
       <c r="AO18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
         <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SCNHTSA-S4</t>
+          <t>SC2-S11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aggressive, Departure</t>
+          <t>Ego merging into an occupied lane</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>The male driver was driving too fast, as well as cutting in and out of traffic, maneuvering the vehicle to the limits of control. The driver lost control of the vehicle and went into a skid. The driver left the roadway and struck the guardrail and then a tree.</t>
+          <t>The lane adjacent to the ego vehicle lane is occupied by slow driving vehicles. The ego vehicle intends to perform a lane change towards the lane in which the other vehicles are driving.</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -3123,7 +3196,7 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -3135,7 +3208,7 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3176,22 +3249,26 @@
       <c r="AI19" t="n">
         <v>1</v>
       </c>
-      <c r="AJ19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sc11.png</t>
+        </is>
+      </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM19" t="n">
         <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
         <v>4</v>
@@ -3200,10 +3277,10 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AR19" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
@@ -3212,17 +3289,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SCNHTSA-S10</t>
+          <t>SC2-S10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ran Red “T- Bone”</t>
+          <t>Ego performing lane change with vehicle behind</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Driver ran the red light. The driver saw the light turn yellow but decided to continue through the intersection. The majority of these crashes occur during daylight hours in urban areas.</t>
+          <t>Another vehicle is driving in the same direction as the ego vehicle, in a lane adjacent to the ego vehicle lane. The ego vehicle intends to perform a lane change towards the lane in which the other vehicle is driving</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -3265,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -3277,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -3318,22 +3395,26 @@
       <c r="AI20" t="n">
         <v>1</v>
       </c>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sc10.png</t>
+        </is>
+      </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Lane Change Scenario</t>
         </is>
       </c>
       <c r="AM20" t="n">
         <v>5</v>
       </c>
       <c r="AN20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AO20" t="n">
         <v>4</v>
@@ -3342,171 +3423,175 @@
         <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AR20" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SC2-S7</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Passable object on intended path</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>The ego vehicle is driving on a road with an object on the intended path of the ego vehicle that is passable, e.g., a manhole lid or a small branch. There are no other vehicles specified. the ego vehicle might swerve around the object, although it also could have driven over it.</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sc7.png</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>Lane Change Scenario</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="n">
         <v>4</v>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SCNHTSA-S6</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rough Road Departure</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Due to the patched and eroded condition of the road surface, the driver lost control of the vehicle and left the roadway.</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>NHTSA</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>Miscellaneous</t>
-        </is>
-      </c>
-      <c r="AM21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>5</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AR21" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SCNHTSA-S12</t>
+          <t>SC2-S20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Inattentive, Ran Stop</t>
+          <t>Oncoming vehicle</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>An inattentive driver in a vehicle, heading north, did not see a stop sign (two-way only) and struck an eastbound vehicle on the passenger's side.</t>
+          <t xml:space="preserve">The ego vehicle is driving straight while another vehicle drives in opposite direction in the same lane. </t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3600,17 +3685,21 @@
         <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sc20.png</t>
+        </is>
+      </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Opposite Direction</t>
         </is>
       </c>
       <c r="AM22" t="n">
@@ -3629,26 +3718,26 @@
         <v>28</v>
       </c>
       <c r="AR22" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SCNHTSA-S8</t>
+          <t>SC2-S21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Impaired, Departure</t>
+          <t>Object on road with oncoming traffic</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>The young (under 25) male driver, who was legally impaired, was driving too fast. He lost control of the vehicle, which left the roadway and overturned. The crash occurred in a rural area between midnight and 2 a.m. on a weekend.</t>
+          <t>The ego vehicle is driving while ap proaching an object on the road, e.g., a parked vehicle. At the same time, a vehicle is approaching in opposite direction. To objective of the ego vehicle is to continue driving straight.</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3670,10 +3759,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3682,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -3744,15 +3833,19 @@
       <c r="AI23" t="n">
         <v>1</v>
       </c>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sc21.png</t>
+        </is>
+      </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Opposite Direction</t>
         </is>
       </c>
       <c r="AM23" t="n">
@@ -3762,35 +3855,36 @@
         <v>14</v>
       </c>
       <c r="AO23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ23" t="n">
         <v>27</v>
       </c>
       <c r="AR23" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SCNHTSA-S16</t>
+          <t>SC2-S28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Left Turn Clip</t>
+          <t>Ego vehicle turns right with oncoming vehicle at sig
+nalized junction</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vehicle A, in an attempt to turn left, cut the corner too sharply and clipped Vehicle B waiting at the intersection. Vehicle A began the turn too early and misjudged the distance between cars.</t>
+          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The ego vehicle turns right at the junction. Another vehicle is approaching the junction from the opposite direction. The other vehicle goes straight at the junction, such that the trajectories of the other vehicle and the ego vehicle intersect. The ego vehicle has to give right of way to the other vehicle.</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3839,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -3854,7 +3948,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3886,22 +3980,26 @@
       <c r="AI24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sc28.png</t>
+        </is>
+      </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Opposite Direction</t>
         </is>
       </c>
       <c r="AM24" t="n">
         <v>5</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AO24" t="n">
         <v>4</v>
@@ -3910,29 +4008,30 @@
         <v>5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AR24" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SCNHTSA-S40</t>
+          <t>SC2-S30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Run Red Into Left Turner</t>
+          <t xml:space="preserve"> Ego vehicle turns right with oncoming vehicle at non
+signalized junction</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A northbound vehicle, A, was waiting to make a left turn. The light changed and A began to turn left. A southbound driver, B, accelerated hard, hoping to make the light and struck Vehicle A.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is not equipped with traffic light signals. The ego vehicle intends to turn right at the junction. Another vehicle is approaching the junction from the opposite direction. The direction that the other vehicle goes to is not specified, i.e., the vehicle could turn left or right or the vehicle could go straight at the junction. </t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3981,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3996,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4023,27 +4122,31 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sc30.png</t>
+        </is>
+      </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Opposite Direction</t>
         </is>
       </c>
       <c r="AM25" t="n">
         <v>5</v>
       </c>
       <c r="AN25" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
@@ -4052,36 +4155,38 @@
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AR25" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SCNHTSA-S30</t>
+          <t>SC2-S44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Passing Clip</t>
+          <t>Pedestrian running a red light</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Vehicle A, in an attempt to pass vehicle B, cut around B, but too closely. Driver A misjudged the distance between cars and clipped the corner of B.</t>
+          <t>The ego vehicle is approaching a pedestrian crossing that is equipped with traffic light signals. The traffic signal for the ego vehicle
+is green. At the same time, a pedestrian is running through the red light. The ego vehicle
+might need to adopt its speed to stay at a safe distance from the pedestrian.</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -4117,7 +4222,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -4126,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4170,22 +4275,26 @@
       <c r="AI26" t="n">
         <v>1</v>
       </c>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>sc44.png</t>
+        </is>
+      </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AO26" t="n">
         <v>4</v>
@@ -4194,36 +4303,37 @@
         <v>5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AR26" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SCNHTSA-S5</t>
+          <t>SC2-S45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slick Road Departure</t>
+          <t>Pedestrian crossing from behind an obstruction</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The driver lost control while driving on an icy, wet road. The driver tried to bring the vehicle back under control by braking and steering. The vehicle spun out and came to rest in the ditch.</t>
+          <t xml:space="preserve">The ego vehicle is driving on a road while a pedestrian crosses the road. The pedestrian is initially outside the view of the ego
+vehicle due to an obstruction. </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -4238,22 +4348,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4312,60 +4422,64 @@
       <c r="AI27" t="n">
         <v>1</v>
       </c>
-      <c r="AJ27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sc45.png</t>
+        </is>
+      </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN27" t="n">
         <v>14</v>
       </c>
       <c r="AO27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AP27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AR27" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SCNHTSA-S41</t>
+          <t>SC2-S40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Misjudgment, Left Turn</t>
+          <t>Pedestrian crossing at zebra crossing</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Vehicle A was waiting to turn left. Driver A observed B approaching from the opposite direction, but thought there was enough time. Driver A misjudged B’s distance and was struck.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a zebra crossing that is not equipped with traffic light signals. At the same time, a pedestrian is crossing the road using the zebra crossing. The ego vehicle has to give right of way to the pedestrian. </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -4401,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -4416,7 +4530,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -4446,30 +4560,34 @@
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sc40.png</t>
+        </is>
+      </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AO28" t="n">
         <v>4</v>
@@ -4478,36 +4596,36 @@
         <v>5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AR28" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SCNHTSA-S27</t>
+          <t>SC2-S39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Aggressive, Rear</t>
+          <t>Jaywalking</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Vehicle A was stopped in traffic. Driver B (at a distance from A) was driving too fast. By the time B realized he/she needed to stop, it was not possible.</t>
+          <t>The ego vehicle is driving on a road with a jaywalker. Although the jaywalker is not allowed to cross the road, the ego vehicle is expected to behave appropriately to avoid critical situations.</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -4543,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -4558,7 +4676,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -4596,22 +4714,26 @@
       <c r="AI29" t="n">
         <v>1</v>
       </c>
-      <c r="AJ29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>sc39.png</t>
+        </is>
+      </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN29" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
         <v>4</v>
@@ -4620,36 +4742,37 @@
         <v>5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AR29" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SCNHTSA-S25</t>
+          <t>SC2-S41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Inattentive, Rear</t>
+          <t xml:space="preserve">Zebra crossing </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A northbound vehicle, A, was stopped waiting at a red traffic signal in an urban area on a major artery. Another vehicle, B, coming from some distance behind, didn't notice that A was stopped and could not stop in time.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a zebra crossing that is not equipped with traffic light signals. There is no pedestrian specified. If
+there is no pedestrian, the ego vehicle is expected to continue driving. </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -4664,10 +4787,10 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4685,7 +4808,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -4700,7 +4823,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -4730,68 +4853,77 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>sc41.png</t>
+        </is>
+      </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AO30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP30" t="n">
         <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SCNHTSA-S42</t>
+          <t>SC2-S48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>View Obstructed Left Turn</t>
+          <t>Pedestrian in same direction obstructed at ego left turn</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vehicle A was stopped in the left lane of a four-lane road. Vehicle C was stopped opposite also turning left. Driver A could see only a short distance past C, thought it was clear, and turned. Vehicle B, in curb lane, struck A head-on.</t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. It is not specified whether the junction is
+equipped with traffic light signals. A pedestrian is approaching the junction from the same
+direction on the left side of the road (from the perspective of the ego vehicle). The pedestrian
+goes straight at the junction such that the trajectories of the ego vehicle and the pedestrian
+intersect. The view from the ego vehicle to the pedestrian is obstructed, e.g., by bushes or
+a hedge.</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -4833,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -4842,7 +4974,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -4872,30 +5004,34 @@
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sc48.png</t>
+        </is>
+      </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO31" t="n">
         <v>4</v>
@@ -4904,36 +5040,38 @@
         <v>5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SCNHTSA-S18</t>
+          <t>SC2-S46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Wave to Go</t>
+          <t>Pedestrian at left turn at non-signalized junction</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>From a driveway, Vehicle A was waiting to make a left turn, but full view of all lanes was not possible due to other traffic. Driver B stopped—leaving a gap—and waved driver A through in front of him. However, Driver C was unaware of this arrangement and crashed into the driver's side of Vehicle A.</t>
+          <t xml:space="preserve">The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. The junction is not equipped with traffic light
+signals. A pedestrian is walking on the left side of the ego vehicle. The walking direction of
+the pedestrian is not specified. </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -4975,7 +5113,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -4984,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -5017,27 +5155,31 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ32" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>sc46.png</t>
+        </is>
+      </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN32" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO32" t="n">
         <v>4</v>
@@ -5046,36 +5188,38 @@
         <v>5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR32" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SCNHTSA-S28</t>
+          <t>SC2-S43</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Pedestrian walking along the road</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Vehicle A was stopped prior to turning when struck by Vehicle B. Driver B stated that the brakes failed to stop the car. Vehicle B was an older vehicle (more than six years).</t>
+          <t xml:space="preserve">The ego vehicle is following the road, approaching a pedestrian that is walking along the road. The ego vehicle should be capable
+to distinguish this principally safe situation from an unsafe situation where the pedestrian
+is about to cross the road. </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -5090,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -5099,7 +5243,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -5111,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -5126,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -5156,68 +5300,76 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>sc43.png</t>
+        </is>
+      </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN33" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AO33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP33" t="n">
         <v>5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AR33" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SCNHTSA-S14</t>
+          <t>SC2-S42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Looked but Didn’t See</t>
+          <t>Pedestrian stationary at road side</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vehicle A was turning right at a two-way stop sign. The driver did not see Vehicle B approaching from lateral direction as Vehicle A turned into the lane. Upon turning, Vehicle A was struck by Vehicle B.</t>
+          <t>The ego vehicle is following the road, approaching a pedestrian standing still at the road side. As the pedestrian is stationary,
+standing still, the ego vehicle should be capable to distinguish this principally safe situation
+from an unsafe situation where the pedestrian is about to cross the road. It is expected
+that the ego vehicle does not act (by braking or steering) upon the presence of the standstill
+pedestrian.</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -5232,13 +5384,13 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5253,7 +5405,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -5274,7 +5426,7 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5301,65 +5453,74 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sc42.png</t>
+        </is>
+      </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN34" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AO34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AP34" t="n">
         <v>5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AR34" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SCNHTSA-S35</t>
+          <t>SC2-S47</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Back Track Front</t>
+          <t>Pedestrian at left turn at signalized junction</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Vehicle A stopped too far out in an intersection. Driver A did not see Vehicle B and backed up to allow other traffic through, striking Vehicle B.</t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. The junction is equipped with traffic light
+signals. A pedestrian is walking on the left side of the ego vehicle. The walking direction of
+the pedestrian is not specified. Therefore, the pedestrian might walk towards the ego vehicle,
+in the same direction, or perpendicular to the ego vehicle, etc. Because the pedestrian is
+initially on the left side of the ego vehicle while the ego vehicle intends to turn left, it might
+be possible that the trajectories of the pedestrian and the ego vehicle intersect</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -5374,10 +5535,10 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5401,7 +5562,7 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -5428,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5448,164 +5609,178 @@
       <c r="AI35" t="n">
         <v>0</v>
       </c>
-      <c r="AJ35" t="inlineStr"/>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>sc47.png</t>
+        </is>
+      </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN35" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AO35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP35" t="n">
         <v>5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AR35" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>47</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SC2-S49</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Pedestrian at right turn at non-signalized junction</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is not equipped with traffic
+light signals. A pedestrian is walking on the right side of the ego vehicle. The walking
+direction of the pedestrian is not specified. Therefore, the pedestrian might walk towards
+the ego vehicle, in the same direction, or perpendicular to the ego vehicle, etc. Because the
+pedestrian is initially on the right side of the ego vehicle while the ego vehicle intends to
+turn right, it might be possible that the trajectories of the pedestrian and the ego vehicle
+intersect.</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sc49.png</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>Pedestrian Interaction</t>
+        </is>
+      </c>
+      <c r="AM36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN36" t="n">
         <v>7</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SCNHTSA-S9</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Back Into Object</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Vehicle A was backing out of a driveway and struck Vehicle B that was parked along the side of the road. Driver A did not see the other vehicle.</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>NHTSA</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>Miscellaneous</t>
-        </is>
-      </c>
-      <c r="AM36" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>4</v>
       </c>
       <c r="AO36" t="n">
         <v>4</v>
@@ -5614,36 +5789,41 @@
         <v>5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR36" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SCNHTSA-S20</t>
+          <t>SC2-S50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Back into Roadway</t>
+          <t>Pedestrian at right turn at signalized junction</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Driver A backed vehicle into roadway. Driver A did not see vehicle B heading west.</t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is equipped with traffic light
+signals. A pedestrian is walking on the right side of the ego vehicle. The walking direction of
+the pedestrian is not specified. Therefore, the pedestrian might walk towards the ego vehicle,
+in the same direction, or perpendicular to the ego vehicle, etc. Because the pedestrian is
+initially on the right side of the ego vehicle while the ego vehicle intends to turn right, it
+might be possible that the trajectories of the pedestrian and the ego vehicle intersect</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -5700,7 +5880,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5712,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5724,30 +5904,34 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ37" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>sc50.png</t>
+        </is>
+      </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Pedestrian Interaction</t>
         </is>
       </c>
       <c r="AM37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN37" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO37" t="n">
         <v>4</v>
@@ -5756,33 +5940,35 @@
         <v>5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR37" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SCNHTSA-S24</t>
+          <t>SC2-S67</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pedal Miss</t>
+          <t>Cyclist turning right and ends up in lane of ego vehicle</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Driver A was attempting to stop behind Vehicle B when Driver A's foot missed the brake pedal and Vehicle A struck Vehicle B from behind.</t>
+          <t>The ego vehicle and a cyclist approach a non-signalized junction. The cyclist is coming from the right side of the ego vehicle. The
+ego vehicle intends to go straight while the cyclist turns right at the junction, such that the
+ego vehicle and the cyclist end up in the same lane.</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -5791,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -5821,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -5845,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5869,27 +6055,31 @@
         <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ38" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sc67.png</t>
+        </is>
+      </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO38" t="n">
         <v>4</v>
@@ -5898,33 +6088,35 @@
         <v>5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AR38" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SCNHTSA-S15</t>
+          <t>SC2-S51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sirens</t>
+          <t>Cyclist crossing from the left side at non-signalized junction</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A police car, with lights and siren on, slowed to cross through an intersection with a red light. Another vehicle was on the crossing road and did not see the approaching police car.</t>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is not equipped with traffic
+light signals. A cyclist is approaching the junction from the left of the ego vehicle. The
+trajectories of the ego vehicle and the cyclist intersect.</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -5933,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -5963,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -5987,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -6008,30 +6200,34 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr"/>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>sc51.png</t>
+        </is>
+      </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>NHTSA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Cyclist Interaction</t>
         </is>
       </c>
       <c r="AM39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO39" t="n">
         <v>4</v>
@@ -6040,152 +6236,4141 @@
         <v>5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AR39" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
+        <v>50</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SC2-S52</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Cyclist crossing from right side at non-signalized junction</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is not equipped with traffic
+light signals. A cyclist is approaching the junction from the right of the ego vehicle. The
+trajectories of the ego vehicle and the cyclist intersect.</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>sc52.png</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL40" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>51</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SC2-S53</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Cyclist crossing from left side at signalized junction</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is equipped with traffic light
+signals. A cyclist is approaching the junction from the left of the ego vehicle. The trajectories
+of the ego vehicle and the cyclist intersect.</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>sc53.png</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL41" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>52</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SC2-S54</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Cyclist crossing from right side at signalized junction</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to go straight. The junction is equipped with traffic
+light signals. A cyclist is approaching the junction from the right of the ego vehicle. The
+trajectories of the ego vehicle and the cyclist intersect.</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sc54.png</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>53</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SC2-S55</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ego vehicle approaching cyclist riding in same direction</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is driving towards a cyclist that is riding in the same direction. The initial intention of the ego vehicle is to drive
+straight. To safely pass the cyclist, the ego vehicle might need to divert its path. Another
+possibility is that the ego vehicle brakes such that the ego vehicle stays behind the cyclist.
+</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sc55.png</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>55</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SC2-S57</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Cyclist and ego vehicle driving in opposite direction</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is driving in the opposite direction of a cyclist. Therefore, the ego vehicle is expected to slow down or to stop when
+the cyclist is passing the ego vehicle, although the initial objective of the ego vehicle is to
+continue driving. </t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>sc57.png</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>64</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SC2-S66</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Cyclist turning left and ends up in lane of ego vehicle</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>The ego vehicle and a cyclist approach a non-signalized junction. The cyclist is coming from the left side of the ego vehicle. The
+ego vehicle intends to go straight while the cyclist turns left at the junction, such that the
+ego vehicle and the cyclist end up in the same lane.</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sc66.png</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>61</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SC2-S63</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Entering a roundabout with a cyclist</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is approaching a roundabout. There is a cyclist on the roundabout or a cyclist is approaching the roundabout
+from another direction. In any case, because the junction is a roundabout, the other vehicle
+approaches the ego vehicle from the right. </t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sc63.png</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>54</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SC2-S56</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ego vehicle driving alongside a cyclist</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>The ego vehicle is driving straight while a cyclist is riding on the left side of the road in the same direction as the ego vehicle. This
+might be because the ego vehicle is overtaking a cyclist. Alternatively, it is also possible
+that the cyclist overtakes the ego vehicle from the left. To prevent a collision between the
+ego vehicle and the cyclist, the ego vehicle might need to divert its path.</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>sc56.png</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>57</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SC2-S59</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Cyclist at left turn at signalized junction</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. The junction is equipped with traffic light
+signals. A cyclist is riding on the left side of the ego vehicle. The riding direction of the
+cyclist is not specified. Therefore, the cyclist might ride towards the ego vehicle, in the same
+direction, or perpendicular to the ego vehicle, etc. Because the cyclist is initially on the left
+side of the ego vehicle while the ego vehicle intends to turn left, it might be possible that
+the trajectories of the cyclist and the ego vehicle intersect.</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>sc59.png</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>58</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SC2-S60</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Cyclist driving in same direction obstructed at ego left turn</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. It is not specified whether the junction is
+equipped with traffic light signals. A cyclist is approaching the junction from the same
+direction on the left side of the road (from the perspective of the ego vehicle). The cyclist
+goes straight at the junction such that the trajectories of the ego vehicle and the cyclist
+intersect. The view from the ego vehicle to the cyclist is obstructed, e.g., by bushes or a
+hedge.</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>sc60.png</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>56</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SC2-S58</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Cyclist at left turn at non-signalized junction</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is approaching a junction at which the ego vehicle intends to turn left. The junction is not equipped with traffic light
+signals. A cyclist is riding on the left side of the ego vehicle. The riding direction of the
+cyclist is not specified. </t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>sc58.png</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>62</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SC2-S64</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Leaving a roundabout with a cyclist</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>The ego vehicle is leaving a roundabout. There is a cyclist on the roundabout. In case the cyclist does not leave the roundabout at
+the same exit as the ego vehicle does, it might be that the ego vehicle needs to give priority
+to the cyclist.</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sc64.png</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>59</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SC2-S61</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cyclist at right turn at non-signalized junction</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is not equipped with traffic
+light signals. A cyclist is riding on the right side of the ego vehicle. The riding direction
+of the cyclist is not specified. Therefore, the cyclist might ride towards the ego vehicle, in
+the same direction, or perpendicular to the ego vehicle, etc. Because the cyclist is initially
+on the right side of the ego vehicle while the ego vehicle intends to turn right, it might be
+possible that the trajectories of the cyclist and the ego vehicle intersect.</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>sc61.png</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>60</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SC2-S62</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Cyclist at left turn at signalized junction</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction at which the ego vehicle intends to turn right. The junction is equipped with traffic light
+signals. A cyclist is riding on the right side of the ego vehicle. The riding direction of the
+cyclist is not specified. Therefore, the cyclist might ride towards the ego vehicle, in the same
+direction, or perpendicular to the ego vehicle, etc. Because the cyclist is initially on the right
+side of the ego vehicle while the ego vehicle intends to turn right, it might be possible that
+the trajectories of the cyclist and the ego vehicle intersect.</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sc62.png</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Cyclist Interaction</t>
+        </is>
+      </c>
+      <c r="AM53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SC2-S1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Maneuvering a bend</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>The ego vehicle is driving on a curved
+ road.</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sc1.png</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Turning Scenario</t>
+        </is>
+      </c>
+      <c r="AM54" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ54" t="n">
         <v>27</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>SCNHTSA-S29</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Slick Road, Rear</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Vehicle A was braking for stopped traffic. Driver B, coming from some distance behind A, saw the brake lights. When B braked the road was very slick. B did not stop and struck A in the rear.</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>NHTSA</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
+      <c r="AR54" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SC2-S2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Turning left</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>The ego vehicle is turning left at non-signalized junction.</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sc2.png</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Turning Scenario</t>
+        </is>
+      </c>
+      <c r="AM55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SC2-S4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Driving straight</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>The ego vehicle is driving on a straight road.</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sc4.png</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
         <is>
           <t>Miscellaneous</t>
         </is>
       </c>
-      <c r="AM40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
+      <c r="AM56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP56" t="n">
         <v>3</v>
       </c>
-      <c r="AP40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>13</v>
+      <c r="AQ56" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SC2-S3</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Turning Right</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>The ego vehicle is turning right at non-signalized junction.</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>sc3.png</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Turning Scenario</t>
+        </is>
+      </c>
+      <c r="AM57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>15</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SC2-S17</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Stopping at a bus bay</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is approaching a bus bay. The goal of the ego vehicle is to park at the bus bay. </t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>sc17.png</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="AM58" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>17</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SC2-S19</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Driving along a bus bay</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>The ego vehicle passes a bus bay. The goal of the ego vehicle is to continue driving. There might be another vehicle at the bus bay intending to leave the bus bay.</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sc19.png</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="AM59" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>21</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SC2-S23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ego vehicle approaching red traffic light</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is red. The objective of the ego vehicle is to cross the junction, but because the traffic signal is red, the ego vehicle is expected to stop.</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>sc23.png</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Traffic Signal</t>
+        </is>
+      </c>
+      <c r="AM60" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>14</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SC2-S16</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Vehicle backing up into ego vehicle</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Another vehicle is driving in reverse. This could be, for example as shown in Figure 35a, because the vehicle is being parked. It might be the case that the ego vehicle has to respond to the reversing vehicle,</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sc16.png</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="AM61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SC2-S5</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Navigating on an empty roundabout</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is approaching a round about. There are no other actors at the roundabout. The ego vehicle wants to navigate the roundabout in any of the possible directions. </t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>sc5.png</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>Turning Scenario</t>
+        </is>
+      </c>
+      <c r="AM62" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>16</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SC2-S18</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Leaving a bus bay</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>The ego vehicle is initially stationary at a bus bay. The goal of the ego vehicle is to leave the bus bay.</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>sc18.png</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="AM63" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>22</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SC2-S24</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ego vehicle approaching green traffic light</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is green or turns green. The objective of the ego vehicle is to cross the junction.</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>sc24.png</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Traffic Signal</t>
+        </is>
+      </c>
+      <c r="AM64" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>23</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SC2-S25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ego vehicle approaching amber traffic light</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is amber or turns amber. The objective of the ego vehicle is to cross the junction.</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sc25.png</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>Traffic Signal</t>
+        </is>
+      </c>
+      <c r="AM65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>24</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SC2-S26</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Vehicle running red traffic light</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ego vehicle is approaching a junction that is equipped with traffic light signals. The traffic signal for the ego vehicle is green. Another vehicle is also approaching the junction and its trajectory intersects that of the ego vehicle. The traffic signal for the other vehicle is red. However, the vehicle is running through the red light. </t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>sc26.png</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>Traffic Signal</t>
+        </is>
+      </c>
+      <c r="AM66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>35</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SC2-S37</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Entering a roundabout with another vehicle</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>The ego vehicle is approaching a round about. There is another vehicle on the roundabout or another vehicle is approaching the roundabout from another direction.</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>sc37.png</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="AM67" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
